--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45894</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>46071</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>46093</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>46071</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>44615</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>44505</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45891</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45392</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>45260</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>46027</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45901</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>45405</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45464</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>44750</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>46093</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>46254</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>44993</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44613</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45124</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>46262</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45319</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>44768</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44916</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45744</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45229</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>46076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>44573</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>46202</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45671</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44750</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45212</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>45401</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>45460</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>44649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>44997</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>46064</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>46202</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45854</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>44573</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>44508</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>44830</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>45330</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44776</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>44466</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45373</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>45901</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45820</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44571</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>45937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>45355</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44750</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45994</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45559</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45433</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45313</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>46020</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>45420</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>46058</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>46064</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44889</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>44750</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>45230</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>46098</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>45596</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>46197</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45236</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45062</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45336</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44868</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>45723</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45477</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45825</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>45842</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45706</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>45351</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>44839</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>44477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>44750</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>44725</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>44460</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>44476</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44508</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44714</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44790</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44691</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44571</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44487</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44613</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44488</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44564</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44508</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>44806</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44505</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44497</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44476</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44692</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44601</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44694</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44776</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44776</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44649</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44889</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44501</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44578</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44853</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44573</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44840</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44852</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44599</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44480</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44525</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44728</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44834</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>44802</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44876</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44573</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44781</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44769</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44472</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44648</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44648</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44487</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44558</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44594</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44812</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44497</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44821</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>45385</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45359</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45358</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44907</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>44750</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44513</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45443</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45107</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>45663</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45663</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45631</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45373</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44488</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44956</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45218</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45217</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45530</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45111</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>44901</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45716</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45630</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45054</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45358</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44581</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>44599</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44874</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45307</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44930</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45399</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45643</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44904</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>45356</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45649</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>45357</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44518</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45558</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>44830</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45558</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45702</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44634</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44944</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44855</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44544</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45405</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45638</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>44655</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45197</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45151</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45335</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>45574</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>45399</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>44637</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>44894</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>45693</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45055</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45362</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45257</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44631</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45467</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45698</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>44929</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45385</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45446</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45251</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45559</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>44943</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45558</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45558</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45062</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45098</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45520</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>44608</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45559</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>44875</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45604</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>44997</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45772</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>44951</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>44958</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45309</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>44971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45132</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45632</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45060</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45376</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44516</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>45310</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44826</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45317</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45007</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45007</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>44935</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45376</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>44951</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45889</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>44501</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45540</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>46136</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45975</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45181</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45846</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45937</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45524</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45151</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45008</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45151</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45886</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>44887</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>44617</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>45233</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45386</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45825</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45889</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45889</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45874</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45797</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45890</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>44893</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45917</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45894</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45719</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45804</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>44946</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>45376</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45824</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45895</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45712</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45645</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45663</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>46006</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>44642</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45917</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45901</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45833</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45811</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45903</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45902</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45960</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45932</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45903</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45905</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45091</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45516</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45672</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45203</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45579</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45810</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45076</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45914</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45914</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45914</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>45916</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>44692</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45167</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45818</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45267</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45376</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45090</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45932</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>44648</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45936</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>46146</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>45937</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>44918</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>44698</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45202</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45938</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45940</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45940</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45940</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45050</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45943</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45940</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>45943</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44861</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45943</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45945</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45405</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45945</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45945</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45313</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45407</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45089</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45947</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45645</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44827</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>44831</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45951</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45951</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>46153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45957</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>45957</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>44966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>45958</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45959</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>45959</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>45673</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>44956</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45960</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45960</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45960</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45370</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45964</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45103</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44977</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45302</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45964</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45965</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45971</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45097</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>45313</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45974</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>45243</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45974</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45952</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45978</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45107</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>44966</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45981</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45981</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>45980</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45980</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>45981</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45981</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45985</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45121</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44835</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44958</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45772</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45579</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>45988</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45260</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45988</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45553</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45775</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45992</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45992</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45992</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45992</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>46161</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>44861</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45771</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45748</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>46161</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45404</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45775</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45628</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45766</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45588</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45992</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>45994</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45995</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45994</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>45999</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>45996</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45694</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45996</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>45999</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45999</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45999</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45261</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44704</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44834</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45327</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>46002</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>44621</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>46003</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>46167</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>46167</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>46002</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>45896</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44629</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45881</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>46168</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45615</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45558</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>46168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45359</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>44827</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>44488</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45715</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>46168</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44578</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45723</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>46169</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>46168</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45638</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>46168</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>46168</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>46168</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>46020</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>46020</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44648</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46020</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44755</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>45210</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>44889</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>44476</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44706</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44851</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>44525</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>46036</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>46036</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>46041</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36918,7 +36918,7 @@
         <v>45623</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>45365</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>46174</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>45572</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44907</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>45664</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>46044</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>46044</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>46044</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>46049</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37663,7 +37663,7 @@
         <v>45509</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>45645</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>46051</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>46175</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45937</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>46055</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>44997</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45156</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>45155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>45637</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>46058</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>44572</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>44572</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>46058</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>46177</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46063</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45559</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45202</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>46063</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>44964</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45685</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>46181</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45394</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>46181</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45233</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45415</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>46072</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>46076</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>46184</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>44887</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45230</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>45176</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44876</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45151</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>46086</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>45040</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>46086</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>46086</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45218</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>44866</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>44943</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>45264</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>46190</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>46190</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45195</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>46094</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>46190</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>46093</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45212</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>46191</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>46191</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>46191</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>46196</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>46099</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>46106</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>46198</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45699</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>45173</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>46108</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44935</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>46111</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>46198</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>46198</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>46112</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>46111</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>44621</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>46114</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>44806</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>46114</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>46112</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44496</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>46119</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>44596</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45215</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>44742</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>44916</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45218</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>45440</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45476</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>44845</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45688</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>46010</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45385</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45772</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>44956</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45655</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>44512</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>45257</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>45825</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>44831</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>46246</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45734</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44476</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45176</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45744</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>46251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45579</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45181</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45574</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>44620</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45547</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45079</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45793</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45258</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>44967</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45376</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>44903</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>46251</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>46030</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45180</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45771</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>46255</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45258</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>45008</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>46253</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45643</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45643</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>44495</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45071</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>45386</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>46259</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45645</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>44552</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>45071</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45063</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>45422</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>44592</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>46258</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45583</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45310</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45559</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>46261</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>44552</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>44831</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>44984</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>44914</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>46265</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>45090</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45090</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45098</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>45098</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>44998</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>44943</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>46267</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45575</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45727</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>44596</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>44929</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>44676</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45195</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45198</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45511</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45783</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>45783</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>46273</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45783</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>46273</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>46273</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>46274</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>46059</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45043</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>46279</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>46279</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>46276</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>46279</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>46276</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>46279</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>46280</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45714</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>46280</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>46280</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45792</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>45788</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>45792</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50440,7 +50440,7 @@
         <v>45792</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45737</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>45309</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>45477</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45575</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>46283</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>45684</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>45363</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>45798</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45565</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51175,7 +51175,7 @@
         <v>45201</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45530</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>46283</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>45532</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45800</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>46240</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51618,7 +51618,7 @@
         <v>45722</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45559</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>45378</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>45198</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45541</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45817</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>45817</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45817</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
         <v>45735</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45818</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>45826</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45834</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45775</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45742</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52645,7 +52645,7 @@
         <v>45645</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52718,7 +52718,7 @@
         <v>45861</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45623</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         <v>45785</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45867</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>45880</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53083,7 +53083,7 @@
         <v>45879</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>45881</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53229,7 +53229,7 @@
         <v>44481</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>45671</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>45351</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53448,7 +53448,7 @@
         <v>44466</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         <v>44741</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53594,7 +53594,7 @@
         <v>44623</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>45271</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>44914</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53813,7 +53813,7 @@
         <v>45671</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45721</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>44481</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>45917</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45964</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>46184</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45894</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>46071</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>46093</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44615</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>46071</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>46283</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44505</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45891</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>45392</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>46027</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45901</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>45029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45464</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45851</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45405</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44750</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44993</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>45124</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>46262</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>44613</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>45319</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>46076</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44768</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44573</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45744</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>44916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>46202</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>46282</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44997</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45854</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>45460</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>46064</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>46202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45401</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44649</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44830</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>45230</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>45420</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>46020</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45330</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45477</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>46058</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>46064</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>46098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>45062</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45820</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>44776</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>45373</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>45825</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>45842</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45706</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>45559</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44889</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>45355</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>46197</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>45313</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44750</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45236</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>46202</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>45336</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>45433</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>45596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>44466</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44868</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45723</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44725</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44476</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44508</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44790</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>44691</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>44571</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44487</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>44613</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44585</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44488</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44564</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44508</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44839</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>44806</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>44505</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44832</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44497</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44476</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>44601</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>44694</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44776</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>44649</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>44889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>44501</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>44578</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>44853</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>44573</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44852</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>44599</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>44840</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>44480</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44525</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>44728</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44834</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44802</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>44573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44781</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>44769</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>44472</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44648</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>44648</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>44487</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44558</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>44594</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44821</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44812</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45734</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44488</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45362</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45405</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45376</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>45202</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45385</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45212</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45772</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45097</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45775</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45359</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45197</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>44875</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44929</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45302</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44827</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45748</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44806</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45370</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45317</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45394</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44866</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45702</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45476</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45516</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44861</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45310</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45723</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44887</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>46020</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>46020</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>46020</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45737</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45309</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44894</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45201</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44513</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45530</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45684</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45565</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45363</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45798</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>44944</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45532</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45309</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45477</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45575</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45825</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>44596</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45886</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45811</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>46036</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46036</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45386</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45890</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45357</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45889</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>45889</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45894</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>46041</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45373</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46044</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>46044</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>46044</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45833</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45902</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>45574</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45903</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>46049</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>44907</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45937</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45905</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>46051</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>44893</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44552</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>44943</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>46058</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>46058</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45916</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45914</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45914</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45914</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45800</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44617</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>46063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>46063</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45559</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>46072</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>45356</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45358</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45399</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>45663</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45663</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45722</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45378</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45559</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45932</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>46086</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45936</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>44476</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>46086</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>46086</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45404</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44943</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45071</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>45938</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>45937</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>45940</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45940</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45940</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>45940</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>46094</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45943</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45943</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>46093</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45945</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45176</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>46099</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45198</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45945</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45945</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45766</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45947</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45951</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>46106</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45951</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45623</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>46111</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>44834</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>46108</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>46111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45957</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45541</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>46112</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>46112</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>44916</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45957</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>46114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45960</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>46114</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45960</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>45960</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>46119</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45958</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45959</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45964</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45107</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>44918</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45965</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44958</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>44827</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>44516</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44544</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45971</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45974</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45645</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45735</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45974</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44518</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45817</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45817</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>44581</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45952</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45952</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45978</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45980</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45980</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44998</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45509</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45575</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45981</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45981</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45981</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45530</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45385</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45981</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44951</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45638</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>46010</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45874</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>45615</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>45988</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45988</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45376</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>44755</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45992</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45992</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45992</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45992</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45817</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45630</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>45994</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>45937</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44512</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45151</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45994</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45996</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45189</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45995</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45996</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45999</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45999</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45917</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45999</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>44642</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45797</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45917</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45999</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45195</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45712</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>45896</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45818</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>46002</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45694</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>46002</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45804</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>45932</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>45975</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>46003</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>44855</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45524</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>45688</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45960</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>45889</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>45089</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>46006</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>45540</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45440</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>45825</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>45824</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45846</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44895</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45826</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>44525</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>46136</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>44930</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>45818</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>44620</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>44956</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32560,7 +32560,7 @@
         <v>45810</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>44951</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>45264</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>44851</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>45210</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>46146</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44943</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45233</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>45167</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45834</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>46153</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>44904</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45407</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>45467</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>45060</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45744</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>45553</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45579</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45376</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45771</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45775</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>44476</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>45446</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45716</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>45071</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>46161</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>46161</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>44501</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45180</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45772</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45107</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>46168</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>46168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45645</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45775</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>46168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>46167</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>46168</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>45040</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45715</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>46168</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45257</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>46168</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45742</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45881</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>46168</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>46167</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45151</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45151</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45645</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>46169</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>44831</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>44621</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>44742</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45861</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44997</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45785</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45623</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>46175</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>44488</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>46174</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45867</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45558</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45558</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37305,7 +37305,7 @@
         <v>46177</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45151</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>44946</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45588</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45218</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>46181</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>46181</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>44631</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>44621</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>46184</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>45063</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>45079</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>45156</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>45155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>45558</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45583</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>45643</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>45579</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>44599</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>46191</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>46191</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>46190</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>46190</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>46191</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>46190</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>45719</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>45559</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>44835</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45008</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45638</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>46196</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>44578</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44572</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>44572</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45173</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45218</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45631</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>46198</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45880</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>44552</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>46198</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>46198</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45579</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44648</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45881</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45071</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45181</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45327</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>44692</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>44629</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>45176</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45663</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45558</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45054</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45793</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>46251</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45050</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>46251</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>46030</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>44637</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45547</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>44592</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45098</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>45098</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45215</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>45103</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45090</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>44698</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>45090</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>46253</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>46255</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>44615</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>44655</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45637</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45693</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>46258</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44876</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43180,7 +43180,7 @@
         <v>45698</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>46259</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43326,7 +43326,7 @@
         <v>45195</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>44676</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>46261</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45258</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>44608</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>44826</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45121</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>44704</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45307</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>44706</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45415</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45257</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>46265</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45727</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45233</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>46267</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>44889</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>45260</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45310</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>46274</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44750</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>44596</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>46273</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>44496</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>44967</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>44935</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>44907</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>44830</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>46273</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>46276</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>46276</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>46280</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>46279</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>46280</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>46279</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>44495</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>46280</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45399</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>46279</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46188,7 +46188,7 @@
         <v>45520</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45335</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>45574</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45230</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>46279</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>44889</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>46240</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45772</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45558</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45673</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>46283</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>46282</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45258</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45218</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45685</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44903</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>46283</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45359</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>44845</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45261</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>44648</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>44861</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45572</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>46059</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>46288</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45903</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45964</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45879</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>46273</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>46288</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44874</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>44997</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48539,7 +48539,7 @@
         <v>46288</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48617,7 +48617,7 @@
         <v>45091</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>46288</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45386</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>44901</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>46246</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45604</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>44964</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>44887</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>44914</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>45007</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>45007</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45203</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>44956</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>44831</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>45376</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49722,7 +49722,7 @@
         <v>45111</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>45559</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>44971</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>44977</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45649</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>44958</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45628</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45405</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>44956</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45655</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>45181</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>45422</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45385</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>45643</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45632</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45672</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>44634</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>45664</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45313</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>45217</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>44935</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>45771</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45202</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45076</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>44984</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45243</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>45090</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45376</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45055</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45267</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>44929</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>45559</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52073,7 +52073,7 @@
         <v>45062</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45365</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>45643</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>45008</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45645</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45358</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45645</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45443</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52662,7 +52662,7 @@
         <v>45251</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45313</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52813,7 +52813,7 @@
         <v>45783</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
         <v>45783</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52959,7 +52959,7 @@
         <v>45783</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53032,7 +53032,7 @@
         <v>45511</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>45043</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>45792</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>45792</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>45792</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45788</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>45714</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>44623</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>44481</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53694,7 +53694,7 @@
         <v>45671</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>45351</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53840,7 +53840,7 @@
         <v>44466</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53913,7 +53913,7 @@
         <v>44741</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53986,7 +53986,7 @@
         <v>45271</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>44914</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54132,7 +54132,7 @@
         <v>45671</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54205,7 +54205,7 @@
         <v>45721</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>44481</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45917</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45964</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54502,7 +54502,7 @@
         <v>46184</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,10 +620,10 @@
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -638,32 +638,36 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T2" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="U2" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Gränsticka
 Dunmossa
+Grönhjon
 Kattfotslav
 Motaggsvamp
+Sårläka
 Tallticka
 Ullticka
 Vedskivlav
 Vedtrappmossa
 Barkticka
+Bronshjon
+Granbarkgnagare
 Kornknutmossa
 Platt fjädermossa
 Rostfläck
@@ -733,7 +737,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +865,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +987,7 @@
         <v>45894</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1110,7 @@
         <v>45723</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1229,7 @@
         <v>46071</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1347,7 +1351,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1468,7 +1472,7 @@
         <v>46093</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1597,7 @@
         <v>44615</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1717,7 @@
         <v>46071</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1833,7 +1837,7 @@
         <v>46283</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1953,7 +1957,7 @@
         <v>44505</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2070,7 +2074,7 @@
         <v>45891</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2191,7 @@
         <v>45392</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2311,7 @@
         <v>46027</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2426,7 +2430,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2537,7 +2541,7 @@
         <v>45901</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2647,7 +2651,7 @@
         <v>45029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2757,7 +2761,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2871,7 +2875,7 @@
         <v>45464</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2980,7 +2984,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3094,7 +3098,7 @@
         <v>45851</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3207,7 +3211,7 @@
         <v>45405</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3316,7 +3320,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3430,7 +3434,7 @@
         <v>44750</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3543,7 +3547,7 @@
         <v>44993</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3655,7 +3659,7 @@
         <v>45124</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3763,7 +3767,7 @@
         <v>46262</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3880,7 +3884,7 @@
         <v>44613</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3992,7 +3996,7 @@
         <v>45319</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4108,7 @@
         <v>46076</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4211,7 +4215,7 @@
         <v>44768</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4326,7 @@
         <v>44573</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4433,7 +4437,7 @@
         <v>45744</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4540,7 +4544,7 @@
         <v>44916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4647,7 +4651,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4754,7 +4758,7 @@
         <v>46202</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4865,7 +4869,7 @@
         <v>46282</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4976,7 +4980,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5083,7 +5087,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5189,7 +5193,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5295,7 +5299,7 @@
         <v>44997</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5405,7 +5409,7 @@
         <v>45854</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5511,7 +5515,7 @@
         <v>45460</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5617,7 +5621,7 @@
         <v>46064</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5732,7 @@
         <v>46202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5834,7 +5838,7 @@
         <v>45401</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5940,7 +5944,7 @@
         <v>44649</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6050,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6151,7 +6155,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6256,7 +6260,7 @@
         <v>44830</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6361,7 +6365,7 @@
         <v>45230</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6466,7 +6470,7 @@
         <v>45420</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6575,7 +6579,7 @@
         <v>46020</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6684,7 @@
         <v>45330</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6785,7 +6789,7 @@
         <v>45477</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6890,7 +6894,7 @@
         <v>45901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6995,7 +6999,7 @@
         <v>46058</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7100,7 +7104,7 @@
         <v>46064</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7210,7 +7214,7 @@
         <v>45937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7315,7 +7319,7 @@
         <v>46098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7425,7 +7429,7 @@
         <v>45062</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7530,7 +7534,7 @@
         <v>45820</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7635,7 +7639,7 @@
         <v>44776</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7740,7 +7744,7 @@
         <v>45994</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7849,7 +7853,7 @@
         <v>45373</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7958,7 +7962,7 @@
         <v>45825</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8063,7 +8067,7 @@
         <v>45842</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8168,7 +8172,7 @@
         <v>45706</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8281,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8382,7 +8386,7 @@
         <v>45559</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8487,7 +8491,7 @@
         <v>44889</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8592,7 +8596,7 @@
         <v>45355</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8697,7 +8701,7 @@
         <v>46197</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8806,7 +8810,7 @@
         <v>45313</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8911,7 +8915,7 @@
         <v>44750</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9020,7 +9024,7 @@
         <v>45236</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9125,7 +9129,7 @@
         <v>46202</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9234,7 +9238,7 @@
         <v>45336</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9339,7 +9343,7 @@
         <v>45433</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9444,7 +9448,7 @@
         <v>45596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9553,7 +9557,7 @@
         <v>44466</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9658,7 +9662,7 @@
         <v>44750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9767,7 +9771,7 @@
         <v>44868</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9872,7 +9876,7 @@
         <v>45723</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9977,7 +9981,7 @@
         <v>45351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10082,7 +10086,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10160,7 +10164,7 @@
         <v>44477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10233,7 +10237,7 @@
         <v>44725</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10306,7 +10310,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10379,7 +10383,7 @@
         <v>44476</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10452,7 +10456,7 @@
         <v>44508</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10525,7 +10529,7 @@
         <v>44714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10598,7 +10602,7 @@
         <v>44790</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10671,7 +10675,7 @@
         <v>44691</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10744,7 +10748,7 @@
         <v>44571</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10817,7 +10821,7 @@
         <v>44487</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10890,7 +10894,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10963,7 +10967,7 @@
         <v>44613</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11036,7 +11040,7 @@
         <v>44585</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11109,7 +11113,7 @@
         <v>44488</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11182,7 +11186,7 @@
         <v>44564</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11255,7 +11259,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11328,7 +11332,7 @@
         <v>44508</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11401,7 +11405,7 @@
         <v>44839</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11474,7 +11478,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11547,7 +11551,7 @@
         <v>44806</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11620,7 +11624,7 @@
         <v>44505</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11693,7 +11697,7 @@
         <v>44832</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11766,7 +11770,7 @@
         <v>44497</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11839,7 +11843,7 @@
         <v>44476</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11912,7 +11916,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11985,7 +11989,7 @@
         <v>44601</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12058,7 +12062,7 @@
         <v>44694</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12131,7 +12135,7 @@
         <v>44776</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12204,7 +12208,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12277,7 +12281,7 @@
         <v>44649</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12350,7 +12354,7 @@
         <v>44889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12423,7 +12427,7 @@
         <v>44501</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12496,7 +12500,7 @@
         <v>44578</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12569,7 +12573,7 @@
         <v>44853</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12642,7 +12646,7 @@
         <v>44573</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12715,7 +12719,7 @@
         <v>44852</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12788,7 +12792,7 @@
         <v>44599</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12861,7 +12865,7 @@
         <v>44840</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12934,7 +12938,7 @@
         <v>44480</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13007,7 +13011,7 @@
         <v>44525</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13080,7 +13084,7 @@
         <v>44728</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13153,7 +13157,7 @@
         <v>44834</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13226,7 +13230,7 @@
         <v>44802</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13299,7 +13303,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13372,7 +13376,7 @@
         <v>44573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13445,7 +13449,7 @@
         <v>44781</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13518,7 +13522,7 @@
         <v>44769</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13591,7 +13595,7 @@
         <v>44472</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13664,7 +13668,7 @@
         <v>44648</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13737,7 +13741,7 @@
         <v>44648</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13810,7 +13814,7 @@
         <v>44487</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13883,7 +13887,7 @@
         <v>44558</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13956,7 +13960,7 @@
         <v>44594</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14029,7 +14033,7 @@
         <v>44821</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14102,7 +14106,7 @@
         <v>44812</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14180,7 +14184,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14253,7 +14257,7 @@
         <v>44497</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14326,7 +14330,7 @@
         <v>45734</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14399,7 +14403,7 @@
         <v>44488</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14472,7 +14476,7 @@
         <v>45362</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14545,7 +14549,7 @@
         <v>45405</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14618,7 +14622,7 @@
         <v>45376</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14691,7 +14695,7 @@
         <v>45202</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14764,7 +14768,7 @@
         <v>45385</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14842,7 +14846,7 @@
         <v>45212</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14915,7 +14919,7 @@
         <v>45772</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14988,7 +14992,7 @@
         <v>45097</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15061,7 +15065,7 @@
         <v>45775</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15134,7 +15138,7 @@
         <v>45359</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15207,7 +15211,7 @@
         <v>45197</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15280,7 +15284,7 @@
         <v>44875</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15353,7 +15357,7 @@
         <v>44929</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15431,7 +15435,7 @@
         <v>45302</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15504,7 +15508,7 @@
         <v>44827</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15577,7 +15581,7 @@
         <v>45748</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15655,7 +15659,7 @@
         <v>44806</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15728,7 +15732,7 @@
         <v>45370</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15801,7 +15805,7 @@
         <v>45317</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15874,7 +15878,7 @@
         <v>45394</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15947,7 +15951,7 @@
         <v>44866</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16020,7 +16024,7 @@
         <v>45702</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16093,7 +16097,7 @@
         <v>45476</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16166,7 +16170,7 @@
         <v>45516</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16244,7 +16248,7 @@
         <v>44861</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16317,7 +16321,7 @@
         <v>45310</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16390,7 +16394,7 @@
         <v>45723</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16463,7 +16467,7 @@
         <v>44887</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16541,7 +16545,7 @@
         <v>46020</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16614,7 +16618,7 @@
         <v>46020</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16687,7 +16691,7 @@
         <v>46020</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16760,7 +16764,7 @@
         <v>45737</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16833,7 +16837,7 @@
         <v>45309</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16906,7 +16910,7 @@
         <v>44894</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16979,7 +16983,7 @@
         <v>45201</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17052,7 +17056,7 @@
         <v>44513</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17125,7 +17129,7 @@
         <v>45530</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17198,7 +17202,7 @@
         <v>45684</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17271,7 +17275,7 @@
         <v>45565</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17344,7 +17348,7 @@
         <v>45363</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17417,7 +17421,7 @@
         <v>45798</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17495,7 +17499,7 @@
         <v>44944</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17568,7 +17572,7 @@
         <v>45532</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17641,7 +17645,7 @@
         <v>45309</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17714,7 +17718,7 @@
         <v>45477</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17787,7 +17791,7 @@
         <v>45575</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17860,7 +17864,7 @@
         <v>45825</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17933,7 +17937,7 @@
         <v>44596</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18006,7 +18010,7 @@
         <v>45886</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18079,7 +18083,7 @@
         <v>45811</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18152,7 +18156,7 @@
         <v>46036</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18225,7 +18229,7 @@
         <v>46036</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18298,7 +18302,7 @@
         <v>45386</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18371,7 +18375,7 @@
         <v>45890</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18444,7 +18448,7 @@
         <v>45357</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18517,7 +18521,7 @@
         <v>45889</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18590,7 +18594,7 @@
         <v>45889</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18663,7 +18667,7 @@
         <v>45894</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18736,7 +18740,7 @@
         <v>46041</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18814,7 +18818,7 @@
         <v>45373</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18887,7 +18891,7 @@
         <v>45895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18960,7 +18964,7 @@
         <v>46044</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19038,7 +19042,7 @@
         <v>46044</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19116,7 +19120,7 @@
         <v>46044</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19194,7 +19198,7 @@
         <v>45833</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19267,7 +19271,7 @@
         <v>45901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19340,7 +19344,7 @@
         <v>45902</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19413,7 +19417,7 @@
         <v>45574</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19486,7 +19490,7 @@
         <v>45903</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19559,7 +19563,7 @@
         <v>46049</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19632,7 +19636,7 @@
         <v>44907</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19705,7 +19709,7 @@
         <v>45937</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19778,7 +19782,7 @@
         <v>45905</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19851,7 +19855,7 @@
         <v>46051</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19924,7 +19928,7 @@
         <v>44893</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19997,7 +20001,7 @@
         <v>44552</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20070,7 +20074,7 @@
         <v>44943</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20143,7 +20147,7 @@
         <v>46058</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20216,7 +20220,7 @@
         <v>46058</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20289,7 +20293,7 @@
         <v>45916</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20362,7 +20366,7 @@
         <v>45914</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20435,7 +20439,7 @@
         <v>45914</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20508,7 +20512,7 @@
         <v>45914</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20581,7 +20585,7 @@
         <v>45800</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20654,7 +20658,7 @@
         <v>44617</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20732,7 +20736,7 @@
         <v>46063</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20805,7 +20809,7 @@
         <v>46063</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20878,7 +20882,7 @@
         <v>45559</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20951,7 +20955,7 @@
         <v>46072</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21024,7 +21028,7 @@
         <v>45356</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21097,7 +21101,7 @@
         <v>45358</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21170,7 +21174,7 @@
         <v>45399</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21243,7 +21247,7 @@
         <v>45663</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21316,7 +21320,7 @@
         <v>45663</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21389,7 +21393,7 @@
         <v>45722</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21462,7 +21466,7 @@
         <v>45378</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21535,7 +21539,7 @@
         <v>45559</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21608,7 +21612,7 @@
         <v>45932</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21681,7 +21685,7 @@
         <v>46086</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21754,7 +21758,7 @@
         <v>45936</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21827,7 +21831,7 @@
         <v>44476</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21900,7 +21904,7 @@
         <v>46086</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21973,7 +21977,7 @@
         <v>46086</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22046,7 +22050,7 @@
         <v>45404</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22119,7 +22123,7 @@
         <v>44943</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22192,7 +22196,7 @@
         <v>45071</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22265,7 +22269,7 @@
         <v>45938</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22338,7 +22342,7 @@
         <v>45937</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22411,7 +22415,7 @@
         <v>45940</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22484,7 +22488,7 @@
         <v>45940</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22557,7 +22561,7 @@
         <v>45940</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22635,7 +22639,7 @@
         <v>45940</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22713,7 +22717,7 @@
         <v>46094</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22786,7 +22790,7 @@
         <v>45943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22859,7 +22863,7 @@
         <v>45943</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22932,7 +22936,7 @@
         <v>45943</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23005,7 +23009,7 @@
         <v>46093</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23083,7 +23087,7 @@
         <v>45945</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23156,7 +23160,7 @@
         <v>45176</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23229,7 +23233,7 @@
         <v>46099</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23302,7 +23306,7 @@
         <v>45198</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23375,7 +23379,7 @@
         <v>45945</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23448,7 +23452,7 @@
         <v>45945</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23521,7 +23525,7 @@
         <v>45766</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23594,7 +23598,7 @@
         <v>45947</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23667,7 +23671,7 @@
         <v>45951</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23740,7 +23744,7 @@
         <v>46106</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23818,7 +23822,7 @@
         <v>45951</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23891,7 +23895,7 @@
         <v>45623</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23964,7 +23968,7 @@
         <v>46111</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24037,7 +24041,7 @@
         <v>44834</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24115,7 +24119,7 @@
         <v>46108</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24188,7 +24192,7 @@
         <v>46111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24261,7 +24265,7 @@
         <v>45957</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24334,7 +24338,7 @@
         <v>45541</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24407,7 +24411,7 @@
         <v>46112</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24485,7 +24489,7 @@
         <v>46112</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24563,7 +24567,7 @@
         <v>44916</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24641,7 +24645,7 @@
         <v>45957</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24714,7 +24718,7 @@
         <v>46114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24787,7 +24791,7 @@
         <v>45960</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24860,7 +24864,7 @@
         <v>46114</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24933,7 +24937,7 @@
         <v>45960</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25006,7 +25010,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25079,7 +25083,7 @@
         <v>45960</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25152,7 +25156,7 @@
         <v>46119</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25225,7 +25229,7 @@
         <v>45958</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25298,7 +25302,7 @@
         <v>45959</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25371,7 +25375,7 @@
         <v>45964</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25444,7 +25448,7 @@
         <v>45107</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25517,7 +25521,7 @@
         <v>44918</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25590,7 +25594,7 @@
         <v>45965</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25663,7 +25667,7 @@
         <v>44958</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25736,7 +25740,7 @@
         <v>44827</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25809,7 +25813,7 @@
         <v>44516</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25882,7 +25886,7 @@
         <v>44544</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25955,7 +25959,7 @@
         <v>45971</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26028,7 +26032,7 @@
         <v>45974</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26106,7 +26110,7 @@
         <v>45645</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26179,7 +26183,7 @@
         <v>45735</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26252,7 +26256,7 @@
         <v>45974</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26325,7 +26329,7 @@
         <v>44518</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26398,7 +26402,7 @@
         <v>45817</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26476,7 +26480,7 @@
         <v>45817</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26549,7 +26553,7 @@
         <v>44581</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26622,7 +26626,7 @@
         <v>45952</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26695,7 +26699,7 @@
         <v>45952</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26768,7 +26772,7 @@
         <v>45978</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26841,7 +26845,7 @@
         <v>45980</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26914,7 +26918,7 @@
         <v>45980</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26987,7 +26991,7 @@
         <v>44998</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27060,7 +27064,7 @@
         <v>45509</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27133,7 +27137,7 @@
         <v>45575</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27206,7 +27210,7 @@
         <v>45981</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27284,7 +27288,7 @@
         <v>45981</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27362,7 +27366,7 @@
         <v>45981</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27435,7 +27439,7 @@
         <v>45530</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27508,7 +27512,7 @@
         <v>45385</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27581,7 +27585,7 @@
         <v>45981</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27654,7 +27658,7 @@
         <v>44951</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27727,7 +27731,7 @@
         <v>45638</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27800,7 +27804,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27873,7 +27877,7 @@
         <v>46010</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27946,7 +27950,7 @@
         <v>45874</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28019,7 +28023,7 @@
         <v>45615</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28092,7 +28096,7 @@
         <v>45988</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28165,7 +28169,7 @@
         <v>45988</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28243,7 +28247,7 @@
         <v>45376</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28316,7 +28320,7 @@
         <v>44755</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28389,7 +28393,7 @@
         <v>45992</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28462,7 +28466,7 @@
         <v>45992</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28535,7 +28539,7 @@
         <v>45992</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28608,7 +28612,7 @@
         <v>45992</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28681,7 +28685,7 @@
         <v>45817</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28754,7 +28758,7 @@
         <v>45630</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28832,7 +28836,7 @@
         <v>45992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28905,7 +28909,7 @@
         <v>45994</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28978,7 +28982,7 @@
         <v>45937</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29051,7 +29055,7 @@
         <v>44512</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29124,7 +29128,7 @@
         <v>45151</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29197,7 +29201,7 @@
         <v>45994</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29270,7 +29274,7 @@
         <v>45996</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29343,7 +29347,7 @@
         <v>45189</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29416,7 +29420,7 @@
         <v>45995</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29489,7 +29493,7 @@
         <v>45996</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29567,7 +29571,7 @@
         <v>45999</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29640,7 +29644,7 @@
         <v>45999</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29713,7 +29717,7 @@
         <v>45917</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29786,7 +29790,7 @@
         <v>45999</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29859,7 +29863,7 @@
         <v>44642</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29932,7 +29936,7 @@
         <v>45797</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30005,7 +30009,7 @@
         <v>45917</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30078,7 +30082,7 @@
         <v>45999</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30151,7 +30155,7 @@
         <v>45198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30224,7 +30228,7 @@
         <v>45195</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30297,7 +30301,7 @@
         <v>45712</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30370,7 +30374,7 @@
         <v>45896</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30443,7 +30447,7 @@
         <v>45818</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30516,7 +30520,7 @@
         <v>46002</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30589,7 +30593,7 @@
         <v>45694</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30662,7 +30666,7 @@
         <v>46002</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30735,7 +30739,7 @@
         <v>45804</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30808,7 +30812,7 @@
         <v>45932</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30881,7 +30885,7 @@
         <v>45975</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30954,7 +30958,7 @@
         <v>46003</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31027,7 +31031,7 @@
         <v>44855</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31100,7 +31104,7 @@
         <v>45524</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31173,7 +31177,7 @@
         <v>45688</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31246,7 +31250,7 @@
         <v>45960</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31319,7 +31323,7 @@
         <v>45889</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31392,7 +31396,7 @@
         <v>45089</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31465,7 +31469,7 @@
         <v>46006</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31538,7 +31542,7 @@
         <v>45540</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31611,7 +31615,7 @@
         <v>45440</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31684,7 +31688,7 @@
         <v>44966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31757,7 +31761,7 @@
         <v>45825</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31830,7 +31834,7 @@
         <v>45824</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31903,7 +31907,7 @@
         <v>45846</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31976,7 +31980,7 @@
         <v>44895</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32049,7 +32053,7 @@
         <v>45826</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32122,7 +32126,7 @@
         <v>44525</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32195,7 +32199,7 @@
         <v>46136</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32268,7 +32272,7 @@
         <v>44930</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32341,7 +32345,7 @@
         <v>45818</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32414,7 +32418,7 @@
         <v>44620</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32487,7 +32491,7 @@
         <v>44956</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32560,7 +32564,7 @@
         <v>45810</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32633,7 +32637,7 @@
         <v>44951</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32706,7 +32710,7 @@
         <v>44966</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32779,7 +32783,7 @@
         <v>45264</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32852,7 +32856,7 @@
         <v>44851</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32925,7 +32929,7 @@
         <v>45210</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32998,7 +33002,7 @@
         <v>46146</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33071,7 +33075,7 @@
         <v>44943</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33144,7 +33148,7 @@
         <v>45233</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33217,7 +33221,7 @@
         <v>45167</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33290,7 +33294,7 @@
         <v>45834</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33363,7 +33367,7 @@
         <v>46153</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33436,7 +33440,7 @@
         <v>44904</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33509,7 +33513,7 @@
         <v>45407</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33582,7 +33586,7 @@
         <v>45467</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33655,7 +33659,7 @@
         <v>45060</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33728,7 +33732,7 @@
         <v>45744</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33801,7 +33805,7 @@
         <v>45553</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33874,7 +33878,7 @@
         <v>45579</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33947,7 +33951,7 @@
         <v>45376</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34020,7 +34024,7 @@
         <v>45771</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34093,7 +34097,7 @@
         <v>45775</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34166,7 +34170,7 @@
         <v>44476</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34239,7 +34243,7 @@
         <v>45446</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34312,7 +34316,7 @@
         <v>45716</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34385,7 +34389,7 @@
         <v>45071</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34458,7 +34462,7 @@
         <v>46161</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34531,7 +34535,7 @@
         <v>46161</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34604,7 +34608,7 @@
         <v>44501</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34677,7 +34681,7 @@
         <v>45180</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34750,7 +34754,7 @@
         <v>45772</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34823,7 +34827,7 @@
         <v>45107</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34896,7 +34900,7 @@
         <v>46168</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34969,7 +34973,7 @@
         <v>46168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35042,7 +35046,7 @@
         <v>45645</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35115,7 +35119,7 @@
         <v>45775</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35188,7 +35192,7 @@
         <v>46168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35261,7 +35265,7 @@
         <v>46167</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35334,7 +35338,7 @@
         <v>46168</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35407,7 +35411,7 @@
         <v>45040</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35480,7 +35484,7 @@
         <v>45715</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35553,7 +35557,7 @@
         <v>46168</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35626,7 +35630,7 @@
         <v>45257</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35699,7 +35703,7 @@
         <v>46168</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35772,7 +35776,7 @@
         <v>45742</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35845,7 +35849,7 @@
         <v>45881</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35918,7 +35922,7 @@
         <v>46168</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35991,7 +35995,7 @@
         <v>46167</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36064,7 +36068,7 @@
         <v>45151</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36137,7 +36141,7 @@
         <v>45151</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36210,7 +36214,7 @@
         <v>45645</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36283,7 +36287,7 @@
         <v>46169</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36356,7 +36360,7 @@
         <v>44831</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36429,7 +36433,7 @@
         <v>44621</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36502,7 +36506,7 @@
         <v>44742</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36575,7 +36579,7 @@
         <v>45861</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36648,7 +36652,7 @@
         <v>44997</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36721,7 +36725,7 @@
         <v>45785</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36794,7 +36798,7 @@
         <v>45623</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36867,7 +36871,7 @@
         <v>46175</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36940,7 +36944,7 @@
         <v>44488</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37013,7 +37017,7 @@
         <v>46174</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37086,7 +37090,7 @@
         <v>45867</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37159,7 +37163,7 @@
         <v>45558</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37232,7 +37236,7 @@
         <v>45558</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37305,7 +37309,7 @@
         <v>46177</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37383,7 +37387,7 @@
         <v>45151</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37456,7 +37460,7 @@
         <v>45132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37529,7 +37533,7 @@
         <v>44946</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37602,7 +37606,7 @@
         <v>45588</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37675,7 +37679,7 @@
         <v>45218</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37748,7 +37752,7 @@
         <v>46181</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37821,7 +37825,7 @@
         <v>46181</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37894,7 +37898,7 @@
         <v>44631</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37967,7 +37971,7 @@
         <v>44621</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38040,7 +38044,7 @@
         <v>46184</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38113,7 +38117,7 @@
         <v>45063</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38186,7 +38190,7 @@
         <v>45079</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38259,7 +38263,7 @@
         <v>45156</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38332,7 +38336,7 @@
         <v>45155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38405,7 +38409,7 @@
         <v>45558</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38478,7 +38482,7 @@
         <v>45583</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38551,7 +38555,7 @@
         <v>45643</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38624,7 +38628,7 @@
         <v>45579</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38697,7 +38701,7 @@
         <v>44599</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38770,7 +38774,7 @@
         <v>46191</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38843,7 +38847,7 @@
         <v>46191</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38916,7 +38920,7 @@
         <v>46190</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38989,7 +38993,7 @@
         <v>46190</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39062,7 +39066,7 @@
         <v>46191</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39135,7 +39139,7 @@
         <v>46190</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39208,7 +39212,7 @@
         <v>45719</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39281,7 +39285,7 @@
         <v>45559</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39354,7 +39358,7 @@
         <v>44835</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39427,7 +39431,7 @@
         <v>45008</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39500,7 +39504,7 @@
         <v>45638</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39573,7 +39577,7 @@
         <v>46196</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39646,7 +39650,7 @@
         <v>44578</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39719,7 +39723,7 @@
         <v>44572</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39792,7 +39796,7 @@
         <v>44572</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39865,7 +39869,7 @@
         <v>45173</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39938,7 +39942,7 @@
         <v>45218</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40011,7 +40015,7 @@
         <v>45631</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40084,7 +40088,7 @@
         <v>46198</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40157,7 +40161,7 @@
         <v>45880</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40230,7 +40234,7 @@
         <v>44552</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40303,7 +40307,7 @@
         <v>46198</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40376,7 +40380,7 @@
         <v>46198</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40449,7 +40453,7 @@
         <v>45579</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40522,7 +40526,7 @@
         <v>44648</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40595,7 +40599,7 @@
         <v>45881</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40668,7 +40672,7 @@
         <v>45071</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40741,7 +40745,7 @@
         <v>45181</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40814,7 +40818,7 @@
         <v>45327</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40907,7 +40911,7 @@
         <v>44692</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40980,7 +40984,7 @@
         <v>44629</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41053,7 +41057,7 @@
         <v>45176</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41126,7 +41130,7 @@
         <v>45663</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41199,7 +41203,7 @@
         <v>45558</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41272,7 +41276,7 @@
         <v>45054</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41345,7 +41349,7 @@
         <v>45793</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41418,7 +41422,7 @@
         <v>46251</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41491,7 +41495,7 @@
         <v>45050</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41564,7 +41568,7 @@
         <v>45098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41637,7 +41641,7 @@
         <v>46251</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41715,7 +41719,7 @@
         <v>46030</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41788,7 +41792,7 @@
         <v>44637</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41861,7 +41865,7 @@
         <v>45547</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41934,7 +41938,7 @@
         <v>44592</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42007,7 +42011,7 @@
         <v>44831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42080,7 +42084,7 @@
         <v>45098</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42153,7 +42157,7 @@
         <v>45098</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42226,7 +42230,7 @@
         <v>45215</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42299,7 +42303,7 @@
         <v>45103</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42372,7 +42376,7 @@
         <v>45090</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42445,7 +42449,7 @@
         <v>44698</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42518,7 +42522,7 @@
         <v>45090</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42591,7 +42595,7 @@
         <v>46253</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42664,7 +42668,7 @@
         <v>46255</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42737,7 +42741,7 @@
         <v>44615</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42810,7 +42814,7 @@
         <v>44655</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42883,7 +42887,7 @@
         <v>45637</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42956,7 +42960,7 @@
         <v>45693</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43029,7 +43033,7 @@
         <v>46258</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43102,7 +43106,7 @@
         <v>44876</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43180,7 +43184,7 @@
         <v>45698</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43253,7 +43257,7 @@
         <v>46259</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43326,7 +43330,7 @@
         <v>45195</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43399,7 +43403,7 @@
         <v>44676</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43472,7 +43476,7 @@
         <v>46261</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43550,7 +43554,7 @@
         <v>45258</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43623,7 +43627,7 @@
         <v>44608</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43696,7 +43700,7 @@
         <v>44826</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43769,7 +43773,7 @@
         <v>45121</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43842,7 +43846,7 @@
         <v>44704</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43915,7 +43919,7 @@
         <v>45307</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43988,7 +43992,7 @@
         <v>44706</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44061,7 +44065,7 @@
         <v>45415</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44134,7 +44138,7 @@
         <v>45257</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44207,7 +44211,7 @@
         <v>46265</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44285,7 +44289,7 @@
         <v>45727</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44358,7 +44362,7 @@
         <v>45233</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44431,7 +44435,7 @@
         <v>46267</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44509,7 +44513,7 @@
         <v>44889</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44582,7 +44586,7 @@
         <v>45260</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44655,7 +44659,7 @@
         <v>45310</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44728,7 +44732,7 @@
         <v>46274</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44801,7 +44805,7 @@
         <v>44750</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44874,7 +44878,7 @@
         <v>44596</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44947,7 +44951,7 @@
         <v>46273</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45020,7 +45024,7 @@
         <v>44496</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45093,7 +45097,7 @@
         <v>44967</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45166,7 +45170,7 @@
         <v>44935</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45239,7 +45243,7 @@
         <v>44907</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45312,7 +45316,7 @@
         <v>44830</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45385,7 +45389,7 @@
         <v>46273</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45458,7 +45462,7 @@
         <v>46276</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45531,7 +45535,7 @@
         <v>46276</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45604,7 +45608,7 @@
         <v>46280</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45677,7 +45681,7 @@
         <v>46279</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45750,7 +45754,7 @@
         <v>46280</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45823,7 +45827,7 @@
         <v>46279</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45896,7 +45900,7 @@
         <v>44495</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45969,7 +45973,7 @@
         <v>46280</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46042,7 +46046,7 @@
         <v>45399</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46115,7 +46119,7 @@
         <v>46279</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46188,7 +46192,7 @@
         <v>45520</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46261,7 +46265,7 @@
         <v>45335</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46334,7 +46338,7 @@
         <v>45574</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46407,7 +46411,7 @@
         <v>45230</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46480,7 +46484,7 @@
         <v>46279</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46553,7 +46557,7 @@
         <v>44889</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46626,7 +46630,7 @@
         <v>46240</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46704,7 +46708,7 @@
         <v>45772</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46777,7 +46781,7 @@
         <v>45558</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46850,7 +46854,7 @@
         <v>45673</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46923,7 +46927,7 @@
         <v>46283</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46996,7 +47000,7 @@
         <v>46282</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47069,7 +47073,7 @@
         <v>45258</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47142,7 +47146,7 @@
         <v>45218</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47215,7 +47219,7 @@
         <v>45685</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47288,7 +47292,7 @@
         <v>44903</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47361,7 +47365,7 @@
         <v>46283</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47434,7 +47438,7 @@
         <v>45359</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47507,7 +47511,7 @@
         <v>44845</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47580,7 +47584,7 @@
         <v>45261</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47653,7 +47657,7 @@
         <v>44648</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47726,7 +47730,7 @@
         <v>44861</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47799,7 +47803,7 @@
         <v>45572</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47872,7 +47876,7 @@
         <v>46059</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47945,7 +47949,7 @@
         <v>46288</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48023,7 +48027,7 @@
         <v>45903</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48096,7 +48100,7 @@
         <v>45964</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48169,7 +48173,7 @@
         <v>45879</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48242,7 +48246,7 @@
         <v>46273</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48320,7 +48324,7 @@
         <v>46288</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48393,7 +48397,7 @@
         <v>44874</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48466,7 +48470,7 @@
         <v>44997</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48539,7 +48543,7 @@
         <v>46288</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48617,7 +48621,7 @@
         <v>45091</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48690,7 +48694,7 @@
         <v>46288</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48768,7 +48772,7 @@
         <v>45386</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48841,7 +48845,7 @@
         <v>44901</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48914,7 +48918,7 @@
         <v>46246</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48987,7 +48991,7 @@
         <v>45604</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49060,7 +49064,7 @@
         <v>44964</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49133,7 +49137,7 @@
         <v>44887</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49206,7 +49210,7 @@
         <v>44914</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49279,7 +49283,7 @@
         <v>45007</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49352,7 +49356,7 @@
         <v>45007</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49425,7 +49429,7 @@
         <v>45203</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49503,7 +49507,7 @@
         <v>44956</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49576,7 +49580,7 @@
         <v>44831</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49649,7 +49653,7 @@
         <v>45376</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49722,7 +49726,7 @@
         <v>45111</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49795,7 +49799,7 @@
         <v>45559</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49868,7 +49872,7 @@
         <v>44971</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49941,7 +49945,7 @@
         <v>44977</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50014,7 +50018,7 @@
         <v>45649</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50087,7 +50091,7 @@
         <v>44958</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50160,7 +50164,7 @@
         <v>45628</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50233,7 +50237,7 @@
         <v>45405</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50306,7 +50310,7 @@
         <v>44956</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50379,7 +50383,7 @@
         <v>45655</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50452,7 +50456,7 @@
         <v>45181</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50525,7 +50529,7 @@
         <v>45422</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50598,7 +50602,7 @@
         <v>45385</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50676,7 +50680,7 @@
         <v>45643</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50749,7 +50753,7 @@
         <v>45632</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50822,7 +50826,7 @@
         <v>45672</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50895,7 +50899,7 @@
         <v>44634</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50968,7 +50972,7 @@
         <v>45664</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51041,7 +51045,7 @@
         <v>45313</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51114,7 +51118,7 @@
         <v>45217</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51192,7 +51196,7 @@
         <v>44935</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51265,7 +51269,7 @@
         <v>45771</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51338,7 +51342,7 @@
         <v>45202</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51411,7 +51415,7 @@
         <v>45076</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51484,7 +51488,7 @@
         <v>44984</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51557,7 +51561,7 @@
         <v>45243</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51630,7 +51634,7 @@
         <v>45090</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51703,7 +51707,7 @@
         <v>45376</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51776,7 +51780,7 @@
         <v>45055</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51849,7 +51853,7 @@
         <v>45267</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51922,7 +51926,7 @@
         <v>44929</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52000,7 +52004,7 @@
         <v>45559</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52073,7 +52077,7 @@
         <v>45062</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52146,7 +52150,7 @@
         <v>45365</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52219,7 +52223,7 @@
         <v>45643</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52292,7 +52296,7 @@
         <v>45008</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52365,7 +52369,7 @@
         <v>45645</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52438,7 +52442,7 @@
         <v>45358</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52511,7 +52515,7 @@
         <v>45645</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52584,7 +52588,7 @@
         <v>45443</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52662,7 +52666,7 @@
         <v>45251</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52740,7 +52744,7 @@
         <v>45313</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52813,7 +52817,7 @@
         <v>45783</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52886,7 +52890,7 @@
         <v>45783</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52959,7 +52963,7 @@
         <v>45783</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53032,7 +53036,7 @@
         <v>45511</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53110,7 +53114,7 @@
         <v>45043</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53183,7 +53187,7 @@
         <v>45792</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53256,7 +53260,7 @@
         <v>45792</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53329,7 +53333,7 @@
         <v>45792</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53402,7 +53406,7 @@
         <v>45788</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53475,7 +53479,7 @@
         <v>45714</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53548,7 +53552,7 @@
         <v>44623</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53621,7 +53625,7 @@
         <v>44481</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53694,7 +53698,7 @@
         <v>45671</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53767,7 +53771,7 @@
         <v>45351</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53840,7 +53844,7 @@
         <v>44466</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53913,7 +53917,7 @@
         <v>44741</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53986,7 +53990,7 @@
         <v>45271</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54059,7 +54063,7 @@
         <v>44914</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54132,7 +54136,7 @@
         <v>45671</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54205,7 +54209,7 @@
         <v>45721</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54283,7 +54287,7 @@
         <v>44481</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54356,7 +54360,7 @@
         <v>45917</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54429,7 +54433,7 @@
         <v>45964</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54502,7 +54506,7 @@
         <v>46184</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45894</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46071</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>46093</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>46262</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>46071</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>44615</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>46283</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>44505</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45392</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46027</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>45405</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>46093</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>45464</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>45851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>46254</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44993</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44613</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>45319</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44768</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>46076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44916</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>44573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45744</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46202</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>46282</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>45854</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44649</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>44997</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>46064</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>46202</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44830</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44776</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45723</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>46020</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45901</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45477</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>46058</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>46064</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>45937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45825</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45994</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45842</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>45373</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45706</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45820</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45355</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44750</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>45559</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44889</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45433</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45313</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>46197</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45420</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44750</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45230</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45236</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>46251</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45062</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45336</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44868</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>45351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44725</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44476</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44508</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44790</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44691</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44571</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44487</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44613</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44585</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>44488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>44564</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44839</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44806</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44508</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44505</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>44832</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44497</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44476</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44601</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>44694</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44776</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44649</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44501</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>44578</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>44853</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44573</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44840</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>44852</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44599</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>44480</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44525</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44728</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44834</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44802</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44781</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44769</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>44472</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>44648</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44648</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44487</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44594</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>44821</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44558</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>44497</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>44812</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44488</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45358</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45443</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44615</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45359</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44874</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45385</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45631</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44750</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>44513</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45107</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45373</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44956</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45218</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44907</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45663</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45663</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45217</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45530</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45716</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44581</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45358</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>44599</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45630</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45111</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45307</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45054</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44930</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45399</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44944</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>46002</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45558</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44830</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45558</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>46003</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45643</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45811</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44904</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45356</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>46002</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45357</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45896</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45702</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45714</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45649</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>44518</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>44634</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>44855</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45405</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45723</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45386</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45889</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>46020</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>46020</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44544</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45889</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>46020</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45890</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45894</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45901</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45833</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44655</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45638</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45903</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45335</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45902</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>46036</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45792</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45197</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45151</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45905</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>46041</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45788</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45574</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45792</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45792</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45737</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45309</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45477</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>46044</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46044</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45575</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>46044</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45399</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>44637</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45914</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45914</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45914</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>46049</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45684</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45363</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45916</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45798</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45565</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45201</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45530</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45532</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45800</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>46051</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45937</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>44894</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45257</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45693</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45055</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45362</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>44631</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45385</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45467</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45698</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45722</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>46058</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>44929</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>46058</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>46063</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45251</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45932</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>46063</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45936</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45446</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45937</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45938</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45559</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45940</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45940</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45940</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>45943</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45940</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>46072</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45943</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45943</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45559</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45378</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45945</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>45945</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45945</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>44943</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>45558</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45558</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45071</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45947</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45951</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45198</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45951</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45062</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45541</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45957</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45957</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>46086</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46086</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>46086</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>45958</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>44889</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45959</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45959</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45098</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>45520</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>44875</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>44997</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45772</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45960</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45960</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45960</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45817</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44608</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45559</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>45604</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>44951</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>44958</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45964</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45817</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>46094</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>46093</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45309</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45971</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>46099</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45632</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45817</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45132</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>45735</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45974</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46106</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45060</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45952</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45818</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45981</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>45981</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>45980</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45981</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45376</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44516</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46108</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45310</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45981</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45007</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45007</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>46111</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>46112</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45985</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>46111</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>44826</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>46114</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>46114</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>46112</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45317</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45988</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>44935</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>46119</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45988</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45992</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45992</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45992</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45992</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44951</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45992</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45994</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45995</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45994</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44501</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45999</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45996</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>45996</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45999</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45999</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45826</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45181</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45999</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45151</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45008</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45151</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44887</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44617</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45233</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45834</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>44893</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45688</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45719</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44946</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45376</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>46010</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45645</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45663</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44512</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45825</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45376</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45091</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45516</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45672</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45889</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45540</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>46136</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45975</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>45846</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>45775</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45203</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45937</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45524</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45579</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>45076</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45874</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45797</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45917</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44692</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45804</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45824</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45712</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>45167</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45267</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45742</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>46006</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>44642</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>45917</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45376</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>45645</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35210,7 +35210,7 @@
         <v>45861</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35283,7 +35283,7 @@
         <v>45960</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45932</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>45090</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45623</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45785</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>44648</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>45867</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45810</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44918</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>44698</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45202</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45050</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>44861</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>45405</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>45313</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>45407</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>45818</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45089</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>45645</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>44827</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44831</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46146</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>44966</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>45673</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46153</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>44956</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45370</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>45103</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>44977</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45302</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45579</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45553</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>46161</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45097</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45771</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46161</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45775</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45313</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45243</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45107</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44966</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>46167</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>46167</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45881</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>46168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>46168</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45121</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>44835</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45880</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44958</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45715</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46169</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46168</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46168</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46168</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>46168</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45772</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45881</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45260</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>46174</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45775</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44861</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45748</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>46175</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45886</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45825</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45404</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45628</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45766</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>46177</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45588</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46181</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>46181</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>46184</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>45694</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45261</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>44704</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>44834</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45327</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>44621</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46190</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46190</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46190</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44629</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>46191</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>46191</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>46191</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>46196</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45615</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45558</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45359</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44827</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>44488</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>46198</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>44578</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45638</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>46198</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>46198</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>44648</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>44755</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>45210</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>44889</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44476</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>44706</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>44851</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>44525</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45793</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>46030</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45623</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45365</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>45572</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>44907</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45664</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>46259</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45509</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45645</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>46258</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>44997</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>46261</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>46265</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45156</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>45155</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45637</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>44572</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>44572</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45559</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>45202</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>46267</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44964</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45685</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45394</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45233</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45415</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>46273</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45188,7 +45188,7 @@
         <v>46273</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>44887</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>45230</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>45176</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>46274</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>46279</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>46279</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>46276</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>46279</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>46276</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>44876</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46001,7 +46001,7 @@
         <v>45151</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>46279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>45040</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>46280</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>46280</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>46280</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45218</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>44866</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>44943</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45264</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45195</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>46283</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45212</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>46240</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45903</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45879</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>46273</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45964</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45173</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>44935</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46282</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>46288</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>46288</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>44621</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44806</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>46246</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>44496</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>46288</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>46288</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44596</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48216,7 +48216,7 @@
         <v>45215</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>44742</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>46283</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>44916</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45218</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>45440</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>45476</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>44845</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>46251</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>45385</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>46294</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45772</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49097,7 +49097,7 @@
         <v>44956</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>46253</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>46266</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45655</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45257</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>44831</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>45734</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>46255</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>44476</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45176</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>46059</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45744</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45579</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>46295</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>45181</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>45574</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>46296</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>46296</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>44620</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45547</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45079</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45258</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>44967</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45376</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>44903</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>45180</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45771</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45008</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45643</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45643</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>44495</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45071</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>45386</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45645</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>44552</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45071</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45422</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>44592</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>45583</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45310</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45559</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>44552</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44831</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44984</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>44914</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45090</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45090</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45098</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45098</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>44998</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>44943</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45575</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53122,7 +53122,7 @@
         <v>45727</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>44596</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53268,7 +53268,7 @@
         <v>44929</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>44676</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45195</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>45198</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45511</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45783</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>45783</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45783</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>45043</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>44481</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45671</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45351</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>44741</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>44623</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45271</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54373,7 +54373,7 @@
         <v>44914</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54446,7 +54446,7 @@
         <v>45671</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>45721</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>44481</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>45917</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45964</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>46184</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>45723</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45894</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46071</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46167</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>46093</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>46262</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>46071</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>44615</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>46283</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>44505</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45392</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46027</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>45029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>45405</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>46093</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>45464</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>45851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>46254</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44993</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44613</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>45319</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44768</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>46076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44916</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>44573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45744</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46202</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>46282</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>45854</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44649</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>44997</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>46064</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>46202</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44830</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>45330</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44776</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45723</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>46020</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45901</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45477</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>46058</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>46064</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>45937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>46098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45825</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45994</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45842</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>45373</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45706</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45820</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45355</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44750</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>45559</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44889</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45433</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45313</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>46197</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45420</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44750</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45230</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>45596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45236</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>46251</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45062</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45336</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>44868</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>45351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44839</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44725</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44476</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44508</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44790</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44691</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44571</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44487</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44613</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44585</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>44488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>44564</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44839</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44806</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44508</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44505</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>44832</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44497</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44476</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44601</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>44694</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44776</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44649</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44501</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>44578</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>44853</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44573</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44840</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>44852</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44599</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>44480</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44525</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44728</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44834</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>44802</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44781</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44769</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>44472</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>44648</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44648</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44487</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>44594</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>44821</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44558</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>44497</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>44812</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44488</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>45358</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45443</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44615</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45359</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44874</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45385</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45631</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44750</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>44513</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45107</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45373</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44956</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45218</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44907</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45663</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45663</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45217</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>45530</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45716</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>44581</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45358</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>44599</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45630</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45111</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45307</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45054</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44930</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45399</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44944</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>46002</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45558</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44830</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45558</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>46003</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45643</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45811</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44904</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45356</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>46002</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45357</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45896</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45702</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>45714</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45649</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>44518</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>44634</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>44855</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18086,7 +18086,7 @@
         <v>45405</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45723</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>45386</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45889</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>46020</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>46020</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44544</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>45889</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>46020</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45890</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45894</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45901</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>45833</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44655</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45638</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45903</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45335</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45902</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>46036</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45792</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45197</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45151</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45905</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>46041</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>45788</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>45574</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45792</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45792</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45737</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45309</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45477</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>46044</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46044</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45575</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>46044</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45399</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>44637</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45914</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45914</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45914</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>46049</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45684</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45363</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45916</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45798</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45565</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45201</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45530</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45532</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45800</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>46051</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45937</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>44894</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45257</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45693</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45055</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45362</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>44631</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45385</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45467</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45698</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45722</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>46058</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>44929</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>46058</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>46063</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45251</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45932</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>46063</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45936</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45446</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45937</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45938</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45559</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45940</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45940</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45940</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>45943</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45940</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>46072</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45943</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45943</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45559</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45378</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45945</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>45945</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45945</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>44943</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>45558</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45558</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45071</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45947</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45951</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>45198</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45951</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45062</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45541</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45957</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45957</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>46086</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46086</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>46086</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>45958</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>44889</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45959</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45959</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45098</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>45520</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>44875</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>44997</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45772</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45960</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45960</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45960</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45817</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>44608</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45559</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>45604</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>44951</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>44958</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45964</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45817</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>44971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>46094</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>46093</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45309</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45971</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>46099</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45632</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45817</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45132</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>45735</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45974</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46106</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45060</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>45952</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45818</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45981</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>45981</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>45980</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45981</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45376</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44516</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46108</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45310</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45981</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45007</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45007</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>46111</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>46112</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         <v>45985</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>46111</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>44826</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>46114</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>46114</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29997,7 +29997,7 @@
         <v>46112</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45317</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45988</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>44935</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>46119</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45988</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45992</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45992</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45992</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45992</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>44951</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45992</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45994</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45995</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45994</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44501</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45999</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45996</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>45996</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45999</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45999</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45826</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45181</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45999</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>45151</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>45008</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>45151</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>44887</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>44617</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45233</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45834</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>44893</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45688</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45719</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44946</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45376</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>46010</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45645</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45663</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>44512</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45825</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45376</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45091</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45516</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45672</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45889</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45540</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>46136</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45975</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>45846</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>45775</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45203</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33823,7 +33823,7 @@
         <v>45937</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45524</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>45579</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>45076</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45874</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45797</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45917</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44692</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>45804</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45824</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45712</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>45167</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45267</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45742</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>46006</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>44642</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>45917</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35064,7 +35064,7 @@
         <v>45376</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>45645</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35210,7 +35210,7 @@
         <v>45861</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35283,7 +35283,7 @@
         <v>45960</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45932</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>45090</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45623</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>45785</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>44648</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>45867</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45810</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>44918</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>44698</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45202</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45050</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>44861</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>45405</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>45313</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>45407</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>45818</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45089</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>45645</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>44827</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44831</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46146</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>44966</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>45673</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46153</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>44956</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45370</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>45103</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>44977</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45302</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45579</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>45553</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>46161</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45097</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45771</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46161</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45775</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45313</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45243</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45107</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>44966</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>46167</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>46167</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45881</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>46168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>46168</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45121</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>44835</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45880</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>44958</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45715</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46168</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46169</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46168</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46168</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46168</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>46168</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45772</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45881</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45260</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>46174</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45775</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44861</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45748</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>46175</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45886</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45825</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45404</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45628</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45766</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>46177</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45588</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46181</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>46181</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>46184</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>45694</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45261</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>44704</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>44834</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45327</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>44621</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46190</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46190</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46190</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44629</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>46191</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>46191</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>46191</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>46196</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45615</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45558</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45359</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44827</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>44488</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>46198</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>44578</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45638</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>46198</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>46198</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>44648</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>44755</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>45210</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>44889</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>44476</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>44706</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>44851</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>44525</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45793</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>46030</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45623</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>45365</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>45572</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>44907</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43567,7 +43567,7 @@
         <v>45664</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>46259</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45509</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45645</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>46258</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>44997</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>46261</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>46265</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45156</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>45155</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45637</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>44572</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>44572</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>45559</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>45202</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>46267</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>44964</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45685</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>45394</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45233</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45042,7 +45042,7 @@
         <v>45415</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>46273</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45188,7 +45188,7 @@
         <v>46273</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>44887</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>45230</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>45176</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>46274</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>46279</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>46279</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>46276</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>46279</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>46276</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>44876</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46001,7 +46001,7 @@
         <v>45151</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>46279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>45040</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>46280</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>46280</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>46280</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45218</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>44866</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>44943</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45264</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45195</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>46283</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45212</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>46240</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45903</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45879</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>46273</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45964</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45173</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>44935</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46282</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>46288</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>46288</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>44621</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44806</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>46246</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>44496</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>46288</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>46288</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>44596</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48216,7 +48216,7 @@
         <v>45215</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>44742</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>46283</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>44916</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45218</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>45440</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>45476</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>44845</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>46251</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>45385</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>46294</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45772</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49097,7 +49097,7 @@
         <v>44956</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>46253</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>46266</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45655</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45257</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>44831</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>45734</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>46255</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>44476</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45176</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>46059</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45744</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45579</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>46295</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>45181</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>45574</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>46296</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>46296</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>46296</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>44620</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45547</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45079</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45258</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>44967</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45376</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>44903</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>45180</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45771</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45008</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45643</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45643</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>44495</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45071</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>45386</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45645</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>44552</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45071</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45422</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>44592</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>45583</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45310</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45559</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>44552</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>44831</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44984</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>44914</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45090</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45090</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45098</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45098</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>44998</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>44943</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45575</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53122,7 +53122,7 @@
         <v>45727</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>44596</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53268,7 +53268,7 @@
         <v>44929</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>44676</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45195</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>45198</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45511</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45783</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>45783</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45783</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>45043</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>44481</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45671</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45351</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>44741</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>44623</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45271</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54373,7 +54373,7 @@
         <v>44914</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54446,7 +54446,7 @@
         <v>45671</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>45721</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>44481</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>45917</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45964</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>46184</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46283</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45894</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46071</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>46167</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44615</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>46093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46071</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>46262</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>44505</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45392</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>46027</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45464</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44750</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>45405</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>46093</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>46254</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45319</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44993</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45229</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44768</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>44916</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>45744</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>46076</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>46282</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>46202</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>45460</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44997</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>45854</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45401</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44649</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46064</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>46240</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>46202</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45420</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45230</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>45596</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45330</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44750</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>45901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44571</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45559</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44868</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45355</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>45723</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45477</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45313</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>45062</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45825</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45842</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44750</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45236</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45706</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>46098</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45336</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45994</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45820</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>46020</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45373</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>45433</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>46058</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46064</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>46197</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>46251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>46202</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>45351</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44839</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44725</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44508</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44714</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44790</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44691</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44571</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44487</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44613</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44488</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44564</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44806</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44505</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44480</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44573</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44497</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44525</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44648</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44648</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44601</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44694</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44728</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44834</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44776</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44776</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44802</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44781</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44649</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44889</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44487</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>44501</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44578</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44853</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44573</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44769</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44852</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45385</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44599</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44594</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44558</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44821</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45772</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44812</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44749</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44497</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45775</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44875</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45097</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45167</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45649</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45359</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44958</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45702</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45628</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45405</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45197</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44904</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>44956</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45407</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>45467</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45655</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>45060</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>45744</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45734</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>45181</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45376</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45422</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45385</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>44488</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45362</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45405</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45376</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>45202</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44827</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>44929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45302</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45446</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45643</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45716</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45632</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45672</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>44634</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45071</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45748</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45664</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44501</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45313</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45180</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44806</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45370</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45394</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45772</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45317</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45217</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45107</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44935</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44866</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>45771</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45212</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45645</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45040</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45257</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45476</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45202</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45310</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44984</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45516</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44861</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45243</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45090</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45376</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>44887</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45151</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45151</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45055</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44831</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45825</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44621</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45886</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>44742</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45309</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45267</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45811</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44894</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>44929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44997</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45559</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45386</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45890</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>44513</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45062</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45365</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45643</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44488</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45008</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>44944</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45889</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45889</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45894</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45895</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45833</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45645</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>44596</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45901</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45357</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45358</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45645</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>45443</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45558</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45558</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45151</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45251</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45313</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45373</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45905</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45132</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>44946</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45588</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45218</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45574</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>44907</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>44631</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45916</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44621</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45914</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45914</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>45914</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45783</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45783</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>45783</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>44893</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45511</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45063</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44552</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45079</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45156</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45155</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45558</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45583</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44943</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45643</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45579</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45043</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>44617</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44599</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45559</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45719</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45559</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>44835</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45792</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45792</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45356</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45008</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45788</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>45714</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45638</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>45358</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45399</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44578</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>44572</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45737</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44572</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45663</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45663</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45173</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45218</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45631</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>44552</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45201</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45530</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45404</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45579</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45684</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45565</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45932</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45363</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45798</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45532</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>44648</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>44943</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45309</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45477</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45575</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45936</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45071</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45071</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45181</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45327</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45800</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44692</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44629</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45176</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45663</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45176</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45558</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45054</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45722</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45378</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>45938</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45050</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45559</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45937</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45766</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45098</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>44637</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45940</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45940</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45940</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45940</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45198</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45943</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45943</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45547</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>44592</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45541</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45943</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44831</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45098</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45098</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45945</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45623</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44834</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>45735</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45945</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45945</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>45817</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>45817</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>45215</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45103</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45817</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44916</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45947</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45090</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45818</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>44698</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45090</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>44615</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45826</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44655</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45637</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>44918</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45951</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44958</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>44827</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45693</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>44876</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45698</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44516</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>44544</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>45195</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45951</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>44676</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45957</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45645</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45960</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45960</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45959</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45960</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>45959</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>44518</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>45834</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44581</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45964</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>44998</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45509</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45575</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>44608</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>44826</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45121</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>45965</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>45530</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>45385</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44951</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45638</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>44704</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45615</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45971</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45307</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44755</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45974</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>44706</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45415</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45257</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45775</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>45974</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45630</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45727</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45233</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45151</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45742</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45189</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45645</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>45952</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45952</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45861</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45198</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45195</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45785</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45623</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>45867</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45694</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>44889</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45260</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45978</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>44855</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45310</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45980</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>44750</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44596</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45089</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44496</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>44967</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>44935</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45981</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>44907</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>44830</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45440</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45981</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45981</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>44966</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45880</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45881</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>46094</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>44895</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>45981</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>46093</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44525</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>46099</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>44495</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45399</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45985</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45520</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44930</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45335</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45574</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45230</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>44889</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44620</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45772</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46106</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>44956</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44951</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44966</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45264</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45988</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>45558</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45988</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>46111</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>44851</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>45673</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>46108</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45992</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45992</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45992</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>46111</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>45992</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>46112</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45210</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45258</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46112</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44943</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45233</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45218</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45992</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>46114</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>46114</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45994</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45685</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>46119</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>44903</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45994</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>45359</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45996</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44845</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45995</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45261</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>44648</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>44861</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45996</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45999</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45999</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45999</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45999</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45896</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>45572</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>46002</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>46002</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>44874</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>46003</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>44997</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>46010</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45874</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45091</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45376</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45386</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>44901</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45937</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>44512</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45723</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>46020</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>46020</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>46020</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45604</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>44964</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45917</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>44887</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>44642</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45797</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>45917</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45712</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>45804</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45932</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45975</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>45524</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45688</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45960</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>44914</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>46036</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>46036</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45889</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>46006</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45540</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46041</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45007</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45007</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46044</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45825</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45824</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>46044</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>46044</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45846</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45203</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44956</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>44831</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>46136</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45376</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45111</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>46049</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45559</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45818</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>44971</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>44977</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45937</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45810</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>46051</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>46058</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>46058</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>46146</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>46063</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>46063</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>46072</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46153</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>46086</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>46086</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46086</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>45553</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45579</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>45771</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45775</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>46161</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>46161</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48449,7 +48449,7 @@
         <v>46168</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>46168</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>46168</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>46167</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>46168</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>45715</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>46168</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>46168</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45881</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>46168</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>46167</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>46169</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49325,7 +49325,7 @@
         <v>46175</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>46174</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>46177</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>46181</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>46181</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>46184</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49768,7 +49768,7 @@
         <v>46191</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>46191</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>46190</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>46190</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>46191</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>46190</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>46196</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>46198</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>46198</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>46198</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45793</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46030</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46265</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>46267</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>46274</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>46273</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>46273</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>46276</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46276</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>46280</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>46279</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>46280</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>46279</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>46280</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>46279</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>46279</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>46283</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>46282</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>46288</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45903</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45964</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>45879</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>46273</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>46288</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>46288</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>46288</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>46246</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>46283</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>46266</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>46294</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52723,7 +52723,7 @@
         <v>46296</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>46253</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>46251</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>46059</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>46296</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>46296</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>46295</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>46255</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>46258</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>46259</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>46301</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>46303</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46304</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46261</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>46303</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46303</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>44623</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>44481</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45671</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45351</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>44741</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>45271</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>44914</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45671</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>45721</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>44481</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45917</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>45964</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54787,7 +54787,7 @@
         <v>46184</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46283</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45894</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46071</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>46167</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>44615</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>46093</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46071</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>46262</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>44505</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45392</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>46027</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45901</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45464</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44750</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>45405</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>46093</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>46254</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45319</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44993</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45229</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44768</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>44916</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>45744</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>46076</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>46282</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>46202</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>45460</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44997</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>45854</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>45401</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44649</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>46064</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>46240</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>46202</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45420</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45230</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>45596</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45330</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44750</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>45901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44571</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45559</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44868</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45355</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>45723</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45477</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45313</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>45062</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45825</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45842</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44750</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45236</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45706</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>46098</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45336</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45994</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45820</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>46020</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45373</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>45433</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>46058</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46064</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>46197</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>46251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>46202</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>45351</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44839</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44725</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44508</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44714</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44790</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44691</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44571</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44487</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44613</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44488</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44508</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44564</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44806</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44505</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44480</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44573</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44497</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44692</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44525</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44648</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44648</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44601</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44694</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44728</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44834</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44776</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44776</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44802</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44781</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44649</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44889</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44487</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>44501</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44578</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44853</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44573</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44769</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44852</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45385</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>44599</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>44594</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44558</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44821</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45772</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44812</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44749</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44497</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45775</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44875</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45097</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45167</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45649</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45359</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44958</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45702</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45628</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45405</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45197</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44904</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>44956</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45407</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>45467</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45655</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>45060</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>45744</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45734</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>45181</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45376</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45422</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>45385</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>44488</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45362</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45405</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45376</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>45202</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44827</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>44929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45302</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45446</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45643</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45716</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45632</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45672</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>44634</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>45071</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45748</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45664</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44501</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45313</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45180</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44806</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45370</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45394</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45772</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45317</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45217</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45107</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44935</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44866</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>45771</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45212</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45645</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>45040</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45257</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45476</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45202</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45310</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44984</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45516</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44861</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45243</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45090</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45376</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>44887</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45151</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45151</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45055</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44831</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45825</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44621</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45886</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>44742</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45309</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45267</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45811</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44894</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>44929</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44997</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45559</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45386</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45890</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>44513</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45062</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45365</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45643</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44488</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45008</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>44944</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45889</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45889</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45894</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45895</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45833</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45645</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>44596</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45901</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45357</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45358</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45645</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>45443</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45558</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45558</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45151</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45251</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45313</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45373</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45905</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45132</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>44946</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45588</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45218</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45574</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>44907</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>44631</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45916</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44621</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45914</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45914</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>45914</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45783</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45783</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>45783</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>44893</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45511</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45063</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>44552</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45079</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45156</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45155</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45558</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45583</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44943</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45643</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45579</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45043</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>44617</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44599</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45559</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45719</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45559</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>44835</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45792</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45792</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45356</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45008</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45788</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>45714</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45638</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25689,7 +25689,7 @@
         <v>45358</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45399</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>44578</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>44572</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45737</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44572</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45663</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45663</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45173</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45218</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45631</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>44552</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45201</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45530</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45404</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45579</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45684</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45565</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45932</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45363</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45798</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45532</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>44648</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>44943</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45309</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45477</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45575</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45936</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45071</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45071</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45181</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45327</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45800</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44692</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44629</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45176</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45663</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45176</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45558</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45054</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45722</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45378</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>45938</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45050</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45559</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45937</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45766</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45098</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>44637</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45940</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45940</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45940</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45940</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45198</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45943</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45943</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45547</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>44592</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45541</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45943</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44831</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45098</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45098</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45945</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45623</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44834</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>45735</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45945</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45945</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>45817</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>45817</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>45215</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45103</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45817</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>44916</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45947</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45090</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45818</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>44698</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45090</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>44615</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45826</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45107</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44655</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45637</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>44918</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45951</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44958</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>44827</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45693</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>44876</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>45698</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44516</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>44544</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>45195</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45951</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>44676</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45957</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45645</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45960</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45960</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45959</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45960</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>45959</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>44518</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>45834</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>44581</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45964</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>44998</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45509</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45575</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>44608</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>44826</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45121</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>45965</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>45530</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>45385</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44951</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45638</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>44704</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45615</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45971</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45307</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44755</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45974</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>44706</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45415</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45257</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45775</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>45974</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45630</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45727</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45233</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>45151</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45742</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45189</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45645</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>45952</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>45952</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45861</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45198</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45195</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45785</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>45623</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>45867</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45694</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>44889</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45260</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45978</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>44855</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>45310</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45980</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>44750</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>44596</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45089</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>44496</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>44967</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>44935</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45981</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>44907</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>44830</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>45440</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45981</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45981</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>44966</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45880</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45881</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>46094</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>44895</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>45981</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>46093</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44525</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>46099</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>44495</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45399</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45985</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45520</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44930</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45335</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45574</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45230</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>44889</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>44620</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45772</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46106</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>44956</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>44951</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44966</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45264</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45988</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>45558</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45988</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>46111</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>44851</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>45673</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>46108</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45992</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45992</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45992</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>46111</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>45992</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>46112</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45210</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45258</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46112</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>44943</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45233</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45218</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45992</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>46114</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>46114</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45994</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45685</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>46119</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>44903</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45994</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>45359</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45996</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>44845</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45995</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45261</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>44648</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>44861</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45996</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45999</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>45999</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45999</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45999</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45896</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>45572</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>46002</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>46002</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>44874</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>46003</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>44997</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>46010</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45874</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45091</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45376</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>45386</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>44901</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45937</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>44512</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45723</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>46020</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>46020</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>46020</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45604</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>44964</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45917</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>44887</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>44642</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45797</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>45917</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45712</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>45804</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>45932</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45975</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>45524</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45688</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45960</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>44914</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>46036</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>46036</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45889</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>46006</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45540</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>46041</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45007</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45007</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46044</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45825</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45824</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>46044</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>46044</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45846</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45203</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44956</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46405,7 +46405,7 @@
         <v>44831</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46478,7 +46478,7 @@
         <v>46136</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46551,7 +46551,7 @@
         <v>45376</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45111</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>46049</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45559</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45818</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>44971</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>44977</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45937</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45810</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>46051</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>46058</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>46058</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>46146</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>46063</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>46063</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>46072</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46153</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>46086</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>46086</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46086</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>45553</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45579</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>45771</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         <v>45775</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48303,7 +48303,7 @@
         <v>46161</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>46161</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48449,7 +48449,7 @@
         <v>46168</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>46168</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>46168</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>46167</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>46168</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>45715</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>46168</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>46168</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45881</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>46168</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>46167</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>46169</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49325,7 +49325,7 @@
         <v>46175</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>46174</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>46177</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>46181</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>46181</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>46184</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49768,7 +49768,7 @@
         <v>46191</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>46191</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>46190</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>46190</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>46191</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>46190</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>46196</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>46198</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>46198</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>46198</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45793</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46030</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46265</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>46267</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>46274</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>46273</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>46273</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>46276</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46276</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>46280</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>46279</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>46280</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>46279</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>46280</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>46279</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>46279</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>46283</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>46282</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>46288</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45903</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45964</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>45879</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>46273</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>46288</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>46288</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>46288</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>46246</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>46283</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>46266</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>46294</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52723,7 +52723,7 @@
         <v>46296</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>46253</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>46251</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52942,7 +52942,7 @@
         <v>46059</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53015,7 +53015,7 @@
         <v>46296</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>46296</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>46295</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>46255</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>46258</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>46259</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>46301</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>46303</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>46304</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46261</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>46303</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46303</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>44623</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>44481</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45671</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45351</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>44741</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>45271</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>44914</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45671</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>45721</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>44481</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45917</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>45964</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54787,7 +54787,7 @@
         <v>46184</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46283</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45894</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46071</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>46167</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>46093</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>44615</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46071</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>46262</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>44505</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45392</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>46027</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45901</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45405</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44750</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45464</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46093</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>46254</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>45851</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44993</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44613</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45319</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44768</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>44916</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45744</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45229</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>46076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44573</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>46282</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>46202</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>45460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44997</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>46240</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>46202</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45854</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45330</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44776</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45373</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45820</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44571</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>45355</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45994</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>46020</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44750</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45559</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45433</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>46058</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46064</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44889</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>46098</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>46197</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44750</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45230</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45596</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45236</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>45062</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45336</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>46251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44868</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>46202</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45723</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>45477</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45842</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>45351</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44839</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44725</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44508</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44714</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44790</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44571</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44691</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44613</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44488</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44564</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44572</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44508</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44806</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44505</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44497</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44692</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44601</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44694</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44776</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44649</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44889</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44501</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44578</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44853</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44573</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44852</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44840</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44599</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44525</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44728</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>44802</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44876</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44573</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44769</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44648</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44487</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44558</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44594</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44749</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44812</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44497</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44821</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44488</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44874</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45359</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45385</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45358</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>44750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44513</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45443</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>45373</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45107</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45631</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45663</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45663</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44956</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45217</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45530</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45189</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45218</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45111</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45716</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45630</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44901</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>44581</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45358</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45054</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>44599</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44944</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45307</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44930</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44895</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45558</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44830</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>45558</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45399</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>45649</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44518</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45643</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44904</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45356</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45357</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44634</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45702</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45405</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44855</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45197</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45638</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45151</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45335</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44655</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45399</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>45574</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>44637</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>45693</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45055</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>44894</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45362</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45257</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44631</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44929</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45467</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45698</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45385</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45446</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44943</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45558</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45558</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45559</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45071</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45062</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>44889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45098</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45520</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44875</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>44997</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45772</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>44608</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45559</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45604</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44951</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>44958</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45309</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44971</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45132</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45060</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45632</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45376</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>44516</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45310</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>45007</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45007</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>44826</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45376</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45889</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45540</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>46136</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45975</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45317</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45846</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44935</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45524</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45886</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>44951</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45874</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45797</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45825</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45386</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44501</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45889</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45804</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45824</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45712</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45889</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45181</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45890</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45894</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45895</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45151</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45008</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45151</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>46006</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44642</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45917</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>44887</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44617</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45233</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45960</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45932</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45811</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45901</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45810</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45833</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45903</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>44893</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45902</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45719</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45905</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44946</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45376</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45818</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45645</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45663</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45914</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45914</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45914</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45916</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>46146</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45091</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45516</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45672</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45203</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45579</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>45076</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45932</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>46153</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45936</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45937</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44692</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45167</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45267</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45938</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45940</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45940</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45940</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45943</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45376</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45940</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45943</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45943</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45945</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45945</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45945</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45090</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45947</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>45951</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>45951</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44648</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45957</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45957</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45958</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45959</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45959</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44918</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44698</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45202</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45579</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>45960</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>45960</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45960</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45050</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>44861</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45553</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>45405</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>45964</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>45313</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45407</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>46161</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>45089</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45771</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45965</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>46161</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45645</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>44827</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44831</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45775</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45971</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45974</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45974</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45952</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45952</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45978</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>44966</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>45981</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45981</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45980</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45980</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>45673</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44956</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45981</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45370</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>45985</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45103</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44977</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45302</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46167</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>46167</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45988</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45881</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>46168</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45992</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45992</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>45992</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45097</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>46168</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45992</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45994</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45715</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45995</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45994</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>46168</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45313</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>46169</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45243</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45999</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45996</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45996</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45999</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45999</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45107</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>46168</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44966</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45999</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>46168</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>46168</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>46168</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46002</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>46003</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45121</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44835</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>46002</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>44958</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45896</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45772</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45260</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45775</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>46174</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44861</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45748</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45404</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45628</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45723</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45766</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45588</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>46020</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>46020</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46020</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45694</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45261</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44704</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44834</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>46175</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>46036</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>46036</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>46041</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>45327</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>46177</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>44621</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>46044</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>46044</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>46044</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46049</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>46181</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>44629</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>46051</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45937</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>45615</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>46181</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45558</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45359</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44827</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>44488</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>46058</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46184</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44578</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>46058</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>46063</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45638</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>46063</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>44648</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>44755</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45210</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46072</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44889</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>44706</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44851</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>44525</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>46086</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>46086</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>46086</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>45623</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45365</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>46190</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>46190</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>46190</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45572</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44907</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>46191</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45664</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46191</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>46191</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>46094</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>46093</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>46196</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>46099</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45509</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>45645</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>46106</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44997</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>46198</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45156</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45155</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46108</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45637</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>46111</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>46112</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>46111</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44572</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>44572</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>46114</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>46114</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>46112</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45559</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>46198</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>46198</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>45202</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>46119</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>44964</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45685</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>45394</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45233</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45415</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>44887</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45230</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45176</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45688</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>44876</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45151</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45040</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>46010</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45218</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44512</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>44866</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>45825</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>44943</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45264</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45195</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45793</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>46030</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45212</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45173</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44935</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>44621</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>44806</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44496</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>46273</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>44596</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>46273</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45215</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>46274</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>44742</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>44916</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>46279</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>46279</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>46276</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>45218</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>46279</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45440</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45476</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>46276</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>44845</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>46279</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>46280</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>45385</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45772</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44956</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>46280</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>46280</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45655</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45257</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>44831</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45734</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>46283</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45176</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45744</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45579</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45181</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45903</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>45574</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45879</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>44620</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>46273</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>45547</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45079</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45258</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>44967</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45376</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>45964</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>44903</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45180</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45771</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>46282</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>46288</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>46288</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45258</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>45008</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45643</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45643</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>46246</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>46288</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>46288</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>44495</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>45071</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45386</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45645</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>44552</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>45071</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45063</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45422</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>44592</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45583</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45310</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>45559</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>44552</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>44831</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>46251</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>44984</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>44914</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45090</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>46294</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45090</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45098</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48527,7 +48527,7 @@
         <v>45098</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>44998</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48673,7 +48673,7 @@
         <v>46253</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>46266</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>44943</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45575</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45727</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>46059</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>46295</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>46296</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>46296</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>46296</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>44596</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>44929</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>44676</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>45195</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45198</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>46258</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>46255</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>45511</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>45783</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45783</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>45783</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50226,7 +50226,7 @@
         <v>45043</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>46301</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>46303</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>46259</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50518,7 +50518,7 @@
         <v>45714</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50591,7 +50591,7 @@
         <v>46303</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45792</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>46304</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45788</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>45792</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45792</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51034,7 +51034,7 @@
         <v>45737</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45309</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>46261</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>45477</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45575</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51404,7 +51404,7 @@
         <v>45684</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45363</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45798</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45565</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>45201</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45530</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>46303</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46265</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45532</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>46307</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>46307</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>45800</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>46283</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52363,7 +52363,7 @@
         <v>46308</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45722</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>46267</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45559</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>45378</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45198</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45541</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45817</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45817</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45817</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45735</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>45818</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45826</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>45834</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45775</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45742</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45645</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45861</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>45623</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45785</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>45867</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45880</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>45881</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45671</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45351</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>44741</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>44623</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>45271</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>44914</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>45671</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54563,7 +54563,7 @@
         <v>45721</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45917</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>45964</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54787,7 +54787,7 @@
         <v>46184</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46283</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45894</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46071</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>46167</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>46093</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>44615</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46071</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>46262</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>44505</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45392</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>46027</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>45260</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45901</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45405</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44750</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45464</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>46093</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>46254</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>45851</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44993</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44613</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45319</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44768</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>44916</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45744</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45229</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>46076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44573</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>46282</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>46202</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>45401</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>45460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44649</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44997</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>46064</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>46240</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>46202</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45854</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45330</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44776</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45373</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45820</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44571</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45937</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>45355</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45994</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>46020</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44750</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45559</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45433</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>46058</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46064</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44889</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>46098</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>46197</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44750</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45230</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45596</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45236</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9048,7 +9048,7 @@
         <v>45062</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45336</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>46251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44868</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>46202</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45723</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>45477</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>45825</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45842</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>45351</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44839</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>44725</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44508</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>44714</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44790</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44571</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44691</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44613</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44488</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44564</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44572</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44508</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44806</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44505</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44497</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44692</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44601</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44694</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44776</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44649</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44889</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44501</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44578</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44853</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44573</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44852</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44840</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44599</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44525</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>44728</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>44834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>44802</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44876</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44573</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44769</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44648</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44487</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44558</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44594</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44749</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44812</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44497</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44821</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>44488</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44874</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45359</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45385</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45358</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>44750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44513</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>44907</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45443</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>45373</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45107</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45631</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45663</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45663</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44956</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45217</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45530</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45189</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45218</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45111</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45716</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45630</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44901</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>44581</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45358</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45054</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>44599</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44944</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45307</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44930</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44895</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45558</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44830</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>45558</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45399</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>45649</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44518</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45643</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44904</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45356</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45357</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44634</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45702</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45405</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44855</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>44544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45197</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45638</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45151</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45335</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>44655</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45399</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>45574</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>44637</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>45693</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>45055</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>44894</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45362</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45257</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44631</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44929</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45467</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45698</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45385</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45446</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44943</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45558</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45558</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45559</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45071</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45062</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>44889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45098</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45520</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44875</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>44997</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45772</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>44608</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45559</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45604</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44951</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>44958</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45309</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44971</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45132</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45060</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45632</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45376</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>44516</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>45310</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>45007</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45007</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>44826</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45376</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45889</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>45540</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>46136</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45975</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45317</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45846</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44935</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45524</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45886</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>44951</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45874</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45797</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45825</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45386</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44501</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45889</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45804</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45824</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45712</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45889</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45181</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45890</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45894</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45895</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45151</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45008</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45151</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>46006</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44642</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45917</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>44887</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44617</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45233</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45960</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45932</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45811</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45901</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45810</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45833</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45903</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>44893</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>45902</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45719</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45905</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44946</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45376</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45818</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45645</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>45663</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45914</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>45914</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>45914</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45916</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>46146</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45091</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45516</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45672</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>45203</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45579</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>45076</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45932</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>46153</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45936</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45937</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44692</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45167</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45267</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45938</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45940</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45940</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45940</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45943</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45376</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45940</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45943</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45943</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45945</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>45945</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45945</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45090</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45947</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>45951</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>45951</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44648</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45957</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45957</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45958</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45959</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45959</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44918</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44698</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45202</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>45579</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>45960</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>45960</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45960</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45050</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>44861</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45553</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>45405</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>45964</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>45313</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45407</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>46161</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>45089</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45771</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45965</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>46161</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45645</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>44827</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44831</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45775</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45971</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45974</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>45974</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45952</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45952</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45978</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>44966</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>45981</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45981</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45980</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>45980</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>45673</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44956</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45981</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45370</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>45985</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45103</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44977</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45302</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46167</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>46167</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45988</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45881</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>46168</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45992</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45992</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>45992</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45097</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>46168</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45992</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45994</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>45715</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45995</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>45994</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32206,7 +32206,7 @@
         <v>46168</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32279,7 +32279,7 @@
         <v>45313</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>46169</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>45243</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45999</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45996</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45996</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45999</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45999</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>45107</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>46168</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>44966</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45999</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>46168</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>46168</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>46168</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46002</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>46003</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>45121</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44835</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>46002</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>44958</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45896</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45772</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45260</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45775</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34109,7 +34109,7 @@
         <v>46174</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44861</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>45748</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>45404</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45628</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45723</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45766</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45588</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>46020</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>46020</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46020</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45694</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45261</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>44704</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44834</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>46175</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>46036</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>46036</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>46041</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>45327</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>46177</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>44621</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>46044</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>46044</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>46044</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46049</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>46181</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>44629</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>46051</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45937</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>45615</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>46181</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45558</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45359</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>44827</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>44488</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>46058</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46184</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44578</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>46058</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>46063</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45638</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>46063</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>44648</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>44755</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>45210</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46072</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44889</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>44706</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>44851</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>44525</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37887,7 +37887,7 @@
         <v>46086</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37960,7 +37960,7 @@
         <v>46086</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>46086</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>45623</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45365</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>46190</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38325,7 +38325,7 @@
         <v>46190</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>46190</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45572</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44907</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>46191</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45664</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>46191</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>46191</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>46094</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>46093</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>46196</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39133,7 +39133,7 @@
         <v>46099</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45509</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>45645</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>46106</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>44997</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>46198</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45156</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45155</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>46108</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45637</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>46111</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>46112</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>46111</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44572</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>44572</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>46114</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>46114</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>46112</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45559</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>46198</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>46198</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>45202</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>46119</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>44964</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45685</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>45394</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45233</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45415</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>44887</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45230</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45176</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45688</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>44876</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45151</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45040</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>46010</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45218</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>44512</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>44866</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>45825</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>44943</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45264</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45195</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45793</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>46030</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45212</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45173</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44935</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>44621</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>44806</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>44496</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>46273</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>44596</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>46273</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43100,7 +43100,7 @@
         <v>45215</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>46274</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>44742</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>44916</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>46279</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>46279</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>46276</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43616,7 +43616,7 @@
         <v>45218</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>46279</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45440</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45476</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>46276</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>44845</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>46279</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>46280</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>45385</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45772</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44956</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>46280</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>46280</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45655</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45257</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>44831</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45734</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>46283</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>45176</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45744</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45579</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45181</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45903</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>45574</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45879</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>44620</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>46273</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>45547</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45079</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45258</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>44967</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45376</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>45964</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>44903</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45180</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45771</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>46282</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>46288</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>46288</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45258</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>45008</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45643</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45643</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>46246</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>46288</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>46288</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>44495</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>45071</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45386</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45645</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>44552</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>45071</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>45063</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>45422</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>44592</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45583</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45310</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>45559</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>44552</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>44831</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>46251</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>44984</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>44914</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45090</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>46294</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45090</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45098</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48527,7 +48527,7 @@
         <v>45098</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>44998</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48673,7 +48673,7 @@
         <v>46253</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>46266</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>44943</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45575</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45727</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>46059</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>46295</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>46296</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>46296</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>46296</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>44596</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>44929</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>44676</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>45195</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45198</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>46258</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>46255</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>45511</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>45783</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>45783</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>45783</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50226,7 +50226,7 @@
         <v>45043</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>46301</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>46303</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>46259</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50518,7 +50518,7 @@
         <v>45714</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50591,7 +50591,7 @@
         <v>46303</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>45792</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>46304</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45788</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>45792</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45792</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51034,7 +51034,7 @@
         <v>45737</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45309</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>46261</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>45477</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45575</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51404,7 +51404,7 @@
         <v>45684</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45363</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45798</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45565</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>45201</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45530</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>46303</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46265</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45532</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>46307</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>46307</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>45800</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>46283</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52363,7 +52363,7 @@
         <v>46308</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45722</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>46267</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>45559</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>45378</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45198</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45541</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45817</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45817</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45817</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45735</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>45818</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45826</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>45834</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45775</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>45742</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45645</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45861</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>45623</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45785</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>45867</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45880</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>45881</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>45671</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45351</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>44741</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>44623</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>45271</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>44914</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>45671</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54563,7 +54563,7 @@
         <v>45721</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54641,7 +54641,7 @@
         <v>45917</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>45964</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54787,7 +54787,7 @@
         <v>46184</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46283</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45894</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46071</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>46167</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>46093</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46262</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>46071</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>44615</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>44505</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45392</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>46027</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45901</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45464</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44750</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46093</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45405</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45319</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44993</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>46282</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>46076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>46202</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>44573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>45744</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44768</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>44916</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45401</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>44649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>46064</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>46240</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45854</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45212</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44997</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45230</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45901</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45433</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>45937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45420</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44889</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>46197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>45994</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44868</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>46020</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45723</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45477</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>46058</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45330</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>46251</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>46064</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45825</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45842</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>46098</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>46202</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>45820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>45373</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>46317</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>45062</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44776</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44571</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>45559</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45355</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45313</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44750</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45236</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45336</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45351</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44839</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44725</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44508</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44790</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44691</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44571</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44613</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44564</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44572</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44806</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44505</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44832</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44692</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44497</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44601</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44694</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44776</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44649</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44501</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44578</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44853</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44573</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44852</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>44840</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44599</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44525</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44728</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>44834</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44802</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44876</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44573</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>44769</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44648</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44558</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44997</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44821</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44812</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45825</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44497</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45886</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45811</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45197</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>45386</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45890</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45734</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>45362</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45889</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45091</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>45405</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45894</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45376</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45202</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45895</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45386</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>44901</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45833</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45212</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45901</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>45902</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45385</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45903</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45772</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45604</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>44964</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45905</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>44887</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>46161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>46161</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45916</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45914</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45914</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45914</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>44914</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>46168</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>46168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>46168</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>46167</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>46168</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45715</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>46168</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45007</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45007</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>46168</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45881</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>46168</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>46167</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>46169</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45775</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44875</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45097</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45203</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45932</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44956</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45936</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44831</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45376</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45359</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45111</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45702</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45938</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45559</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45937</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44971</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44977</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45940</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>46175</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45940</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>46174</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45940</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45940</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45943</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45943</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45943</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44827</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>46177</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45945</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44929</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45302</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45649</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>44958</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45748</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44806</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45370</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45394</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45317</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45945</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45945</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>44866</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45947</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45628</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45405</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>44956</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45655</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>46181</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>46181</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45951</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45181</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45422</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45385</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45957</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>46184</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45957</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45643</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45632</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45672</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45959</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44634</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45960</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45664</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45958</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45959</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45313</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45964</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45217</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>44935</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46191</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>46191</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>46190</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46190</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45965</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>46191</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>46190</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45771</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45971</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45202</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46196</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45076</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>44984</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45974</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45243</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45090</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45952</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45952</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45376</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>46198</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45978</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>46198</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>46198</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45980</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45055</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45981</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45267</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45981</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45981</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44929</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45559</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45981</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45476</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45062</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45365</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45985</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45643</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45008</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45645</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45793</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45988</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45988</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>46030</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45310</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45992</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45992</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45992</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45358</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>45992</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45645</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45992</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45994</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45516</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>44861</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45994</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45443</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45996</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45995</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45251</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45313</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45996</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45999</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45999</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45896</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>46002</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>46002</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>46003</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44887</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45783</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45783</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>45783</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45511</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>46280</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>46279</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>46280</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45043</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>46279</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>46280</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>46279</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>46279</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45723</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>46020</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>46020</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>46020</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45792</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45792</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>46283</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>46282</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>45792</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45788</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45714</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>46036</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>46036</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>45737</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>46041</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>46288</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45903</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45964</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45879</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45201</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>46044</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45530</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>46288</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45684</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45565</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>46044</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>46044</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45363</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45798</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45532</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45477</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45575</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>46288</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>46049</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45937</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45800</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>46288</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>46051</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>45309</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>45722</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>46246</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45378</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45559</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>46058</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>46058</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>46266</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>46294</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32600,7 +32600,7 @@
         <v>45198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>44894</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45541</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>46063</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>46063</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45735</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45817</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45817</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45817</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45818</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>46072</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46296</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45826</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>46253</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>46251</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>46296</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>46296</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>46295</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>46086</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>46086</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>46086</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45834</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44513</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>46255</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>46094</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>46258</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46093</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>44944</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46099</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45775</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44596</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>46259</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>46106</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>46301</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45742</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>46111</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45645</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>46108</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>46111</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>46112</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>45861</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>46112</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45357</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>46303</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>46304</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>46114</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>46114</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45785</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45623</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46261</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45867</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>46119</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46303</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>46303</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45880</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45881</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45373</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>46308</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>46265</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45574</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>46307</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>44907</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>46010</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45874</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37317,7 +37317,7 @@
         <v>46307</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45376</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>44893</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>44552</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>44943</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>46267</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45937</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44512</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>44617</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45917</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>44642</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45797</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45917</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45712</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45804</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45932</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45559</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45975</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45524</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45688</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45960</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45889</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45356</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46006</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45540</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45980</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46273</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>46316</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46273</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>46273</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46315</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>46315</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45825</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>46316</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>46316</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45824</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45358</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45846</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45399</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45663</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45663</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46283</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46136</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46059</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46274</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45818</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45404</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>46318</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>46318</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>46318</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>46318</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>46276</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>46276</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45810</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>46318</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>44943</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>46317</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45071</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>46146</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>46318</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>45176</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45766</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>46153</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45623</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>44834</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>44916</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>45553</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>45579</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45771</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45775</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45107</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>44918</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>44958</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>44827</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>44516</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44544</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45645</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44518</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44581</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>44998</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>45509</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45575</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45530</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45385</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>44951</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>45638</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>45615</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>44755</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45630</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45151</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>45189</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45198</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44146,7 +44146,7 @@
         <v>45694</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>44855</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>45089</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45440</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>44966</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>44895</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>44525</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>44930</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>44620</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>44956</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44951</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>44966</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>45264</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>44851</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45168,7 +45168,7 @@
         <v>45210</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>44943</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45233</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45167</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44904</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45407</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45467</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45060</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45744</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45376</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45446</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45716</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45071</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>44501</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45180</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45772</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45107</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45645</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45040</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45257</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>45151</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45151</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>44831</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>44621</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44742</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>44997</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45558</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45558</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45151</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>45132</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>44946</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45588</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45218</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>44631</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>44621</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45063</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45079</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45156</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45155</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45558</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45583</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45643</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45579</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>44599</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45719</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>45559</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44835</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45008</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45638</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44578</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>44572</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>44572</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>45173</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45218</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45631</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>44552</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>45579</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>44648</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45071</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45181</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45327</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>44692</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>44629</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45176</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45663</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45558</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>45054</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45098</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>44637</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45547</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>44592</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>44831</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45098</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>45098</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45215</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45103</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>45090</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>44698</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45090</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51028,7 +51028,7 @@
         <v>44615</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>44655</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45637</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45693</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51320,7 +51320,7 @@
         <v>44876</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45698</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>45195</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>44676</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>45258</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>44608</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>44826</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45121</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>44704</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51982,7 +51982,7 @@
         <v>45307</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>44706</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45415</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45257</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45727</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45233</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>44889</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45260</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>45310</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52639,7 +52639,7 @@
         <v>44750</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>44596</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>44496</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>44967</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>44935</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>44907</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53077,7 +53077,7 @@
         <v>44830</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>44495</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45399</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53296,7 +53296,7 @@
         <v>45520</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         <v>45335</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45574</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45230</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>44889</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45772</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45558</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45673</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45258</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>45218</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>45685</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>44903</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45359</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>44845</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>45261</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>44648</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>44861</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45572</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>44874</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54683,7 +54683,7 @@
         <v>44623</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54756,7 +54756,7 @@
         <v>45671</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54829,7 +54829,7 @@
         <v>45351</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54902,7 +54902,7 @@
         <v>44741</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54975,7 +54975,7 @@
         <v>45271</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55048,7 +55048,7 @@
         <v>44914</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45671</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55194,7 +55194,7 @@
         <v>45721</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55272,7 +55272,7 @@
         <v>45917</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55345,7 +55345,7 @@
         <v>45964</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55418,7 +55418,7 @@
         <v>46184</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>45965</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45138</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45701</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>46283</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>45894</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45723</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46071</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>46167</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>46093</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46262</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>46071</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>44615</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>44505</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45392</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45260</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>46027</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45901</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45029</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45464</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44750</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46093</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>46254</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45851</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>45405</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45319</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>44993</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>46282</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>46076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>46202</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>44573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>45744</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>44768</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>44916</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45229</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45671</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>44750</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45401</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>44649</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>46064</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>46240</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45854</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45212</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44997</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45230</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45901</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>45433</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>45937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45420</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44889</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>46197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>45994</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44868</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>46020</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>45723</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45477</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>46058</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45330</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>46251</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>46064</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>45825</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45842</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>46098</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>46202</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45706</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>45820</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>45373</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>46317</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>45062</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44776</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44571</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>45559</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45355</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45313</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44750</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45236</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45336</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45351</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44839</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44725</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44508</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44790</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44691</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44571</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44613</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44585</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44564</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44572</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44839</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44806</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44508</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44505</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44832</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44692</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44497</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44601</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44694</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44776</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44649</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44501</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44578</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44853</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44573</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44852</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>44840</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44599</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44525</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44728</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>44834</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44802</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44876</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44573</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>44781</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>44769</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44648</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>44594</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44558</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>44997</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>44821</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44812</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45825</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44497</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45886</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45811</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45197</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>45386</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45890</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45734</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>45362</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45889</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45091</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>45405</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45894</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45376</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45202</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45895</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45386</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>44901</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45833</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45212</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>45901</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>45902</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45385</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45903</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45772</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45604</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>44964</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45905</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>44887</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>46161</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>46161</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45916</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45914</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45914</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45914</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>44914</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>46168</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>46168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>46168</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>46167</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>46168</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45715</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>46168</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45007</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45007</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>46168</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45881</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>46168</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>46167</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>46169</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45775</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44875</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45097</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45203</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45932</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44956</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45936</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44831</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45376</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45359</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45111</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45702</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45938</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45559</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45937</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44971</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44977</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45940</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>46175</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45940</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>46174</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45940</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45940</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45943</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45943</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45943</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44827</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>46177</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45945</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44929</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45302</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45649</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>44958</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45748</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>44806</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45370</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>45394</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45317</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45945</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45945</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>44866</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45947</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45628</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45405</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>44956</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45655</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>46181</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>46181</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45951</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45181</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45422</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45385</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45957</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>46184</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45957</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45643</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45632</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45672</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45959</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44634</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45960</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45664</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45958</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45959</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45313</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45964</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45217</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>44935</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46191</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>46191</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>46190</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46190</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45965</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>46191</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>46190</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45771</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45971</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45202</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46196</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45076</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>44984</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45974</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45243</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45090</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45952</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45952</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45376</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>46198</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45978</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>46198</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>46198</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45980</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45055</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45981</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45267</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45981</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45981</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44929</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45559</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45981</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45476</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45062</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45365</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45985</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45643</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45008</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45645</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45793</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45988</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45988</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>46030</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45310</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45992</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45992</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45992</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45358</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>45992</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45645</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45992</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>45994</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>45516</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>44861</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45994</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45443</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45996</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45995</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45251</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45313</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45996</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45999</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45999</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45896</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>46002</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>46002</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>46003</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44887</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45783</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45783</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>45783</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45511</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>46280</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>46279</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>46280</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45043</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>46279</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>46280</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>46279</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>46279</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45723</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>46020</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>46020</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>46020</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45792</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45792</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>46283</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>46282</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>45792</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45788</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45714</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>46036</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>46036</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>45737</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>46041</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>46288</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45903</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45964</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45879</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45201</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>46044</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45530</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>46288</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45684</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45565</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>46044</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>46044</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45363</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45798</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45532</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45309</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45477</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45575</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>46288</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>46049</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45937</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45800</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>46288</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>46051</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>45309</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>45722</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>46246</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45378</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45559</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>46058</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>46058</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>46266</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>46294</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32600,7 +32600,7 @@
         <v>45198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>44894</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45541</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>46063</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>46063</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45735</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45817</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45817</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>45817</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>45818</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>46072</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46296</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45826</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>46253</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>46251</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>46296</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>46296</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>46295</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>46086</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>46086</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>46086</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45834</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44513</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>46255</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>46094</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>46258</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46093</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>44944</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46099</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45775</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44596</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>46259</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>46106</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>46301</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45742</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>46111</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>45645</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>46108</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>46111</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>46112</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>45861</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>46112</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45357</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>46303</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>46304</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>46114</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>46114</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45785</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45623</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46261</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45867</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>46119</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46303</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>46303</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45880</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>45881</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45373</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>46308</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>46265</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45574</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>46307</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>44907</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>46010</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45874</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37317,7 +37317,7 @@
         <v>46307</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45376</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>44893</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>44552</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>44943</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>46267</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45937</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44512</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>44617</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45917</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>44642</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45797</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45917</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45712</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45804</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45932</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45559</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45975</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45524</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45688</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45960</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45889</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45356</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46006</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45540</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>45980</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46273</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>46316</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46273</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>46273</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>46315</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>46315</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45825</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>46316</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>46316</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45824</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45358</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45846</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45399</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45663</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45663</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46283</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46136</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46059</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46274</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45818</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45404</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>46318</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>46318</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>46318</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>46318</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>46276</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>46276</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45810</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>46318</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>44943</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>46317</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45071</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>46146</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>46318</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>45176</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45766</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>46153</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45623</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>44834</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>44916</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>45553</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>45579</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45771</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45775</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45107</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>44918</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>44958</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>44827</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>44516</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>44544</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45645</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>44518</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44581</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>44998</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>45509</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45575</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45530</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45385</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>44951</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>45638</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>45615</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>44755</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>45630</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45151</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>45189</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45198</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44146,7 +44146,7 @@
         <v>45694</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>44855</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44292,7 +44292,7 @@
         <v>45089</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45440</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>44966</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>44895</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>44525</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>44930</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>44620</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>44956</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>44951</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>44966</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>45264</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>44851</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45168,7 +45168,7 @@
         <v>45210</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>44943</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45233</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45167</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44904</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45407</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>45467</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45060</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45744</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45376</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45446</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>45716</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>45071</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>44501</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45180</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45772</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45107</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45645</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45040</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45257</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>45151</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45151</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>44831</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46847,7 +46847,7 @@
         <v>44621</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>44742</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>44997</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45558</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45558</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45151</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>45132</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47358,7 +47358,7 @@
         <v>44946</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45588</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45218</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>44631</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47650,7 +47650,7 @@
         <v>44621</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45063</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45079</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45156</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45155</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45558</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45583</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45643</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45579</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>44599</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45719</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>45559</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44835</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45008</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45638</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44578</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>44572</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>44572</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>45173</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45218</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45631</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>44552</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>45579</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>44648</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45071</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45181</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45327</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>44692</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>44629</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45176</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45663</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45558</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>45054</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45098</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>44637</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45547</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>44592</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>44831</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45098</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>45098</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45215</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45103</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>45090</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>44698</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45090</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51028,7 +51028,7 @@
         <v>44615</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>44655</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51174,7 +51174,7 @@
         <v>45637</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45693</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51320,7 +51320,7 @@
         <v>44876</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45698</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>45195</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>44676</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>45258</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>44608</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>44826</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45121</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>44704</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51982,7 +51982,7 @@
         <v>45307</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>44706</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45415</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45257</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52274,7 +52274,7 @@
         <v>45727</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45233</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>44889</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45260</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>45310</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52639,7 +52639,7 @@
         <v>44750</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>44596</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>44496</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>44967</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>44935</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>44907</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53077,7 +53077,7 @@
         <v>44830</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53150,7 +53150,7 @@
         <v>44495</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>45399</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53296,7 +53296,7 @@
         <v>45520</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         <v>45335</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45574</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45230</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>44889</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45772</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45558</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45673</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45258</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>45218</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54026,7 +54026,7 @@
         <v>45685</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>44903</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45359</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54245,7 +54245,7 @@
         <v>44845</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>45261</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>44648</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>44861</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45572</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>44874</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54683,7 +54683,7 @@
         <v>44623</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54756,7 +54756,7 @@
         <v>45671</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54829,7 +54829,7 @@
         <v>45351</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54902,7 +54902,7 @@
         <v>44741</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54975,7 +54975,7 @@
         <v>45271</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55048,7 +55048,7 @@
         <v>44914</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45671</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55194,7 +55194,7 @@
         <v>45721</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55272,7 +55272,7 @@
         <v>45917</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55345,7 +55345,7 @@
         <v>45964</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55418,7 +55418,7 @@
         <v>46184</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
